--- a/surveyWCknock.xlsx
+++ b/surveyWCknock.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M564"/>
+  <dimension ref="A1:M596"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>r16</t>
+          <t>r4</t>
         </is>
       </c>
     </row>
@@ -11184,12 +11184,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>scoregame89</t>
+          <t>scoregame97</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Round of 16 : Paraguay vs France</t>
+          <t>Quarterfinal : France vs Morocco</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>${round} = 'r16'</t>
+          <t>${round} = 'r4'</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>sumgoalgame89</t>
+          <t>sumgoalgame97</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -11237,12 +11237,12 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>substr(${scoregame89}, 0, 1) + substr(${scoregame89}, 2, 4)</t>
+          <t>substr(${scoregame97}, 0, 1) + substr(${scoregame97}, 2, 4)</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>${round} = 'r16'</t>
+          <t>${round} = 'r4'</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>diffgoalgame89</t>
+          <t>diffgoalgame97</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>substr(${scoregame89}, 0, 1) - substr(${scoregame89}, 2, 4)</t>
+          <t>substr(${scoregame97}, 0, 1) - substr(${scoregame97}, 2, 4)</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>${round} = 'r16'</t>
+          <t>${round} = 'r4'</t>
         </is>
       </c>
     </row>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>resultgamegame89</t>
+          <t>resultgamegame97</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>if(${diffgoalgame89} &gt; 0, 'Paraguay  wins!!! ', if(${diffgoalgame89} = 0, 'Paraguay and France  draw!!! ', if(${diffgoalgame89} &lt; 0, 'France  wins!!!  by  ', 'Please enter a score')))</t>
+          <t>if(${diffgoalgame97} &gt; 0, 'France  wins!!! ', if(${diffgoalgame97} = 0, 'France and Morocco  draw!!! ', if(${diffgoalgame97} &lt; 0, 'Morocco  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>${round} = 'r16'</t>
+          <t>${round} = 'r4'</t>
         </is>
       </c>
     </row>
@@ -11308,17 +11308,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>notegame89</t>
+          <t>notegame97</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>${resultgamegame89} ${scoregame89}</t>
+          <t>${resultgamegame97} ${scoregame97}</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>${round} = 'r16'</t>
+          <t>${round} = 'r4'</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>drawgame89</t>
+          <t>drawgame97</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>selected(${game89}, squad)</t>
+          <t>selected(${game97}, squad)</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>${round} = 'r16' and ${diffgoalgame89} = 0</t>
+          <t>${round} = 'r4' and ${diffgoalgame97} = 0</t>
         </is>
       </c>
     </row>
@@ -11372,17 +11372,17 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>game89</t>
+          <t>game97</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>PRY FRA</t>
+          <t>FRA MAR</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>${round} = 'r16'</t>
+          <t>${round} = 'r4'</t>
         </is>
       </c>
     </row>
@@ -11394,6095 +11394,7147 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
+          <t>game97scorer</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Select scorers</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Select scorers, be careful of the number of goals per team you register.
+For this game you can only select ${sumgoalgame97} players.</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>selected(${game97}, squad)</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>count-selected(.)=${sumgoalgame97}</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Review, you must select only ${sumgoalgame97} players!</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>${round} = 'r4' and ${sumgoalgame97} != 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>scoregame98</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Quarterfinal : Spain vs Belgium</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Register the score in the order of the teams in the title. 
+Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9+]-[0-9+]$')</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>Use the format number-number</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>sumgoalgame98</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>calcsumgoal</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>substr(${scoregame98}, 0, 1) + substr(${scoregame98}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>diffgoalgame98</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>calcdiffgoal</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>substr(${scoregame98}, 0, 1) - substr(${scoregame98}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>resultgamegame98</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>resultgame</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>if(${diffgoalgame98} &gt; 0, 'Spain  wins!!! ', if(${diffgoalgame98} = 0, 'Spain and Belgium  draw!!! ', if(${diffgoalgame98} &lt; 0, 'Belgium  wins!!!  by  ', 'Please enter a score')))</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>notegame98</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>${resultgamegame98} ${scoregame98}</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>select_one country</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>drawgame98</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>As you selected a draw, please enter the winning team at penalty shootout</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>selected(${game98}, squad)</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>Select one team only</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>${round} = 'r4' and ${diffgoalgame98} = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>game98</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>ESP BEL</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>select_multiple players</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>game98scorer</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Select scorers</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Select scorers, be careful of the number of goals per team you register.
+For this game you can only select ${sumgoalgame98} players.</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>selected(${game98}, squad)</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>count-selected(.)=${sumgoalgame98}</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Review, you must select only ${sumgoalgame98} players!</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>${round} = 'r4' and ${sumgoalgame98} != 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>scoregame99</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Quarterfinal : Norway vs England</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Register the score in the order of the teams in the title. 
+Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9+]-[0-9+]$')</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>Use the format number-number</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>sumgoalgame99</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>calcsumgoal</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>substr(${scoregame99}, 0, 1) + substr(${scoregame99}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>diffgoalgame99</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>calcdiffgoal</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>substr(${scoregame99}, 0, 1) - substr(${scoregame99}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>resultgamegame99</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>resultgame</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>if(${diffgoalgame99} &gt; 0, 'Norway  wins!!! ', if(${diffgoalgame99} = 0, 'Norway and England  draw!!! ', if(${diffgoalgame99} &lt; 0, 'England  wins!!!  by  ', 'Please enter a score')))</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>notegame99</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>${resultgamegame99} ${scoregame99}</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>select_one country</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>drawgame99</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>As you selected a draw, please enter the winning team at penalty shootout</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>selected(${game99}, squad)</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Select one team only</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>${round} = 'r4' and ${diffgoalgame99} = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>game99</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>NOR ENG</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>select_multiple players</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>game99scorer</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Select scorers</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Select scorers, be careful of the number of goals per team you register.
+For this game you can only select ${sumgoalgame99} players.</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>selected(${game99}, squad)</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>count-selected(.)=${sumgoalgame99}</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>Review, you must select only ${sumgoalgame99} players!</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>${round} = 'r4' and ${sumgoalgame99} != 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>scoregame100</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Quarterfinal : Argentina vs Switzerland</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Register the score in the order of the teams in the title. 
+Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9+]-[0-9+]$')</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>Use the format number-number</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>sumgoalgame100</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>calcsumgoal</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>substr(${scoregame100}, 0, 1) + substr(${scoregame100}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>diffgoalgame100</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>calcdiffgoal</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>substr(${scoregame100}, 0, 1) - substr(${scoregame100}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>resultgamegame100</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>resultgame</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>if(${diffgoalgame100} &gt; 0, 'Argentina  wins!!! ', if(${diffgoalgame100} = 0, 'Argentina and Switzerland  draw!!! ', if(${diffgoalgame100} &lt; 0, 'Switzerland  wins!!!  by  ', 'Please enter a score')))</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>notegame100</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>${resultgamegame100} ${scoregame100}</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>select_one country</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>drawgame100</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>As you selected a draw, please enter the winning team at penalty shootout</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>selected(${game100}, squad)</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Select one team only</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>${round} = 'r4' and ${diffgoalgame100} = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>game100</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>ARG CHE</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>${round} = 'r4'</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>select_multiple players</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>game100scorer</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Select scorers</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Select scorers, be careful of the number of goals per team you register.
+For this game you can only select ${sumgoalgame100} players.</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>selected(${game100}, squad)</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>count-selected(.)=${sumgoalgame100}</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Review, you must select only ${sumgoalgame100} players!</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>${round} = 'r4' and ${sumgoalgame100} != 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>scoregame89</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Round of 16 : Paraguay vs France</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Register the score in the order of the teams in the title. 
+Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9+]-[0-9+]$')</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Use the format number-number</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>${round} = 'r16'</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>sumgoalgame89</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>calcsumgoal</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>substr(${scoregame89}, 0, 1) + substr(${scoregame89}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>${round} = 'r16'</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>diffgoalgame89</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>calcdiffgoal</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>substr(${scoregame89}, 0, 1) - substr(${scoregame89}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>${round} = 'r16'</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>resultgamegame89</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>resultgame</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>if(${diffgoalgame89} &gt; 0, 'Paraguay  wins!!! ', if(${diffgoalgame89} = 0, 'Paraguay and France  draw!!! ', if(${diffgoalgame89} &lt; 0, 'France  wins!!!  by  ', 'Please enter a score')))</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>${round} = 'r16'</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>notegame89</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>${resultgamegame89} ${scoregame89}</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>${round} = 'r16'</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>select_one country</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>drawgame89</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>As you selected a draw, please enter the winning team at penalty shootout</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>selected(${game89}, squad)</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Select one team only</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>${round} = 'r16' and ${diffgoalgame89} = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>game89</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>PRY FRA</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>${round} = 'r16'</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>select_multiple players</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
           <t>game89scorer</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
+      <c r="C412" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D412" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame89} players.</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr">
+      <c r="G412" t="inlineStr">
         <is>
           <t>selected(${game89}, squad)</t>
         </is>
       </c>
-      <c r="H380" t="inlineStr">
+      <c r="H412" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr">
+      <c r="I412" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame89}</t>
         </is>
       </c>
-      <c r="J380" t="inlineStr">
+      <c r="J412" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame89} players!</t>
         </is>
       </c>
-      <c r="L380" t="inlineStr">
+      <c r="L412" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M380" t="inlineStr">
+      <c r="M412" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame89} != 0</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="413">
+      <c r="A413" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>scoregame90</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
+      <c r="C413" t="inlineStr">
         <is>
           <t>Round of 16 : Canada vs Morocco</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
+      <c r="D413" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I381" t="inlineStr">
+      <c r="I413" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J381" t="inlineStr">
+      <c r="J413" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
+      <c r="L413" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M381" t="inlineStr">
+      <c r="M413" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
+    <row r="414">
+      <c r="A414" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>sumgoalgame90</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr">
+      <c r="K414" t="inlineStr">
         <is>
           <t>substr(${scoregame90}, 0, 1) + substr(${scoregame90}, 2, 4)</t>
         </is>
       </c>
-      <c r="M382" t="inlineStr">
+      <c r="M414" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
+    <row r="415">
+      <c r="A415" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>diffgoalgame90</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr">
+      <c r="K415" t="inlineStr">
         <is>
           <t>substr(${scoregame90}, 0, 1) - substr(${scoregame90}, 2, 4)</t>
         </is>
       </c>
-      <c r="M383" t="inlineStr">
+      <c r="M415" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
+    <row r="416">
+      <c r="A416" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>resultgamegame90</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
+      <c r="C416" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr">
+      <c r="K416" t="inlineStr">
         <is>
           <t>if(${diffgoalgame90} &gt; 0, 'Canada  wins!!! ', if(${diffgoalgame90} = 0, 'Canada and Morocco  draw!!! ', if(${diffgoalgame90} &lt; 0, 'Morocco  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M384" t="inlineStr">
+      <c r="M416" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
+    <row r="417">
+      <c r="A417" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B417" t="inlineStr">
         <is>
           <t>notegame90</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
+      <c r="C417" t="inlineStr">
         <is>
           <t>${resultgamegame90} ${scoregame90}</t>
         </is>
       </c>
-      <c r="M385" t="inlineStr">
+      <c r="M417" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
+    <row r="418">
+      <c r="A418" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>drawgame90</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
+      <c r="D418" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr">
+      <c r="G418" t="inlineStr">
         <is>
           <t>selected(${game90}, squad)</t>
         </is>
       </c>
-      <c r="J386" t="inlineStr">
+      <c r="J418" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L386" t="inlineStr">
+      <c r="L418" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M386" t="inlineStr">
+      <c r="M418" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${diffgoalgame90} = 0</t>
         </is>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
+    <row r="419">
+      <c r="A419" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>game90</t>
         </is>
       </c>
-      <c r="F387" t="inlineStr">
+      <c r="F419" t="inlineStr">
         <is>
           <t>CAN MAR</t>
         </is>
       </c>
-      <c r="M387" t="inlineStr">
+      <c r="M419" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
+    <row r="420">
+      <c r="A420" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>game90scorer</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="D420" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame90} players.</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr">
+      <c r="G420" t="inlineStr">
         <is>
           <t>selected(${game90}, squad)</t>
         </is>
       </c>
-      <c r="H388" t="inlineStr">
+      <c r="H420" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr">
+      <c r="I420" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame90}</t>
         </is>
       </c>
-      <c r="J388" t="inlineStr">
+      <c r="J420" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame90} players!</t>
         </is>
       </c>
-      <c r="L388" t="inlineStr">
+      <c r="L420" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M388" t="inlineStr">
+      <c r="M420" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame90} != 0</t>
         </is>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
+    <row r="421">
+      <c r="A421" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B421" t="inlineStr">
         <is>
           <t>scoregame91</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
+      <c r="C421" t="inlineStr">
         <is>
           <t>Round of 16 : Brazil vs Norway</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
+      <c r="D421" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I389" t="inlineStr">
+      <c r="I421" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J389" t="inlineStr">
+      <c r="J421" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L389" t="inlineStr">
+      <c r="L421" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M389" t="inlineStr">
+      <c r="M421" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
+    <row r="422">
+      <c r="A422" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>sumgoalgame91</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr">
+      <c r="C422" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr">
+      <c r="K422" t="inlineStr">
         <is>
           <t>substr(${scoregame91}, 0, 1) + substr(${scoregame91}, 2, 4)</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr">
+      <c r="M422" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
+    <row r="423">
+      <c r="A423" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>diffgoalgame91</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="C423" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr">
+      <c r="K423" t="inlineStr">
         <is>
           <t>substr(${scoregame91}, 0, 1) - substr(${scoregame91}, 2, 4)</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr">
+      <c r="M423" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
+    <row r="424">
+      <c r="A424" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>resultgamegame91</t>
         </is>
       </c>
-      <c r="C392" t="inlineStr">
+      <c r="C424" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr">
+      <c r="K424" t="inlineStr">
         <is>
           <t>if(${diffgoalgame91} &gt; 0, 'Brazil  wins!!! ', if(${diffgoalgame91} = 0, 'Brazil and Norway  draw!!! ', if(${diffgoalgame91} &lt; 0, 'Norway  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M392" t="inlineStr">
+      <c r="M424" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
+    <row r="425">
+      <c r="A425" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
+      <c r="B425" t="inlineStr">
         <is>
           <t>notegame91</t>
         </is>
       </c>
-      <c r="C393" t="inlineStr">
+      <c r="C425" t="inlineStr">
         <is>
           <t>${resultgamegame91} ${scoregame91}</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr">
+      <c r="M425" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
+    <row r="426">
+      <c r="A426" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B426" t="inlineStr">
         <is>
           <t>drawgame91</t>
         </is>
       </c>
-      <c r="C394" t="inlineStr">
+      <c r="C426" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
+      <c r="D426" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
+      <c r="G426" t="inlineStr">
         <is>
           <t>selected(${game91}, squad)</t>
         </is>
       </c>
-      <c r="J394" t="inlineStr">
+      <c r="J426" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L394" t="inlineStr">
+      <c r="L426" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M394" t="inlineStr">
+      <c r="M426" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${diffgoalgame91} = 0</t>
         </is>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
+    <row r="427">
+      <c r="A427" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
+      <c r="B427" t="inlineStr">
         <is>
           <t>game91</t>
         </is>
       </c>
-      <c r="F395" t="inlineStr">
+      <c r="F427" t="inlineStr">
         <is>
           <t>BRA NOR</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr">
+      <c r="M427" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
+    <row r="428">
+      <c r="A428" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
+      <c r="B428" t="inlineStr">
         <is>
           <t>game91scorer</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
+      <c r="C428" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr">
+      <c r="D428" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame91} players.</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr">
+      <c r="G428" t="inlineStr">
         <is>
           <t>selected(${game91}, squad)</t>
         </is>
       </c>
-      <c r="H396" t="inlineStr">
+      <c r="H428" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr">
+      <c r="I428" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame91}</t>
         </is>
       </c>
-      <c r="J396" t="inlineStr">
+      <c r="J428" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame91} players!</t>
         </is>
       </c>
-      <c r="L396" t="inlineStr">
+      <c r="L428" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr">
+      <c r="M428" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame91} != 0</t>
         </is>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
+    <row r="429">
+      <c r="A429" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B429" t="inlineStr">
         <is>
           <t>scoregame92</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
+      <c r="C429" t="inlineStr">
         <is>
           <t>Round of 16 : Mexico vs England</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr">
+      <c r="D429" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I397" t="inlineStr">
+      <c r="I429" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J397" t="inlineStr">
+      <c r="J429" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
+      <c r="L429" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr">
+      <c r="M429" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
+    <row r="430">
+      <c r="A430" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B430" t="inlineStr">
         <is>
           <t>sumgoalgame92</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
+      <c r="C430" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr">
+      <c r="K430" t="inlineStr">
         <is>
           <t>substr(${scoregame92}, 0, 1) + substr(${scoregame92}, 2, 4)</t>
         </is>
       </c>
-      <c r="M398" t="inlineStr">
+      <c r="M430" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
+    <row r="431">
+      <c r="A431" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
+      <c r="B431" t="inlineStr">
         <is>
           <t>diffgoalgame92</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
+      <c r="C431" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr">
+      <c r="K431" t="inlineStr">
         <is>
           <t>substr(${scoregame92}, 0, 1) - substr(${scoregame92}, 2, 4)</t>
         </is>
       </c>
-      <c r="M399" t="inlineStr">
+      <c r="M431" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
+    <row r="432">
+      <c r="A432" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B432" t="inlineStr">
         <is>
           <t>resultgamegame92</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr">
+      <c r="C432" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr">
+      <c r="K432" t="inlineStr">
         <is>
           <t>if(${diffgoalgame92} &gt; 0, 'Mexico  wins!!! ', if(${diffgoalgame92} = 0, 'Mexico and England  draw!!! ', if(${diffgoalgame92} &lt; 0, 'England  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M400" t="inlineStr">
+      <c r="M432" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
+    <row r="433">
+      <c r="A433" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B433" t="inlineStr">
         <is>
           <t>notegame92</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr">
+      <c r="C433" t="inlineStr">
         <is>
           <t>${resultgamegame92} ${scoregame92}</t>
         </is>
       </c>
-      <c r="M401" t="inlineStr">
+      <c r="M433" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
+    <row r="434">
+      <c r="A434" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>drawgame92</t>
         </is>
       </c>
-      <c r="C402" t="inlineStr">
+      <c r="C434" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
+      <c r="D434" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
+      <c r="G434" t="inlineStr">
         <is>
           <t>selected(${game92}, squad)</t>
         </is>
       </c>
-      <c r="J402" t="inlineStr">
+      <c r="J434" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L402" t="inlineStr">
+      <c r="L434" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M402" t="inlineStr">
+      <c r="M434" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${diffgoalgame92} = 0</t>
         </is>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
+    <row r="435">
+      <c r="A435" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B435" t="inlineStr">
         <is>
           <t>game92</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr">
+      <c r="F435" t="inlineStr">
         <is>
           <t>MEX ENG</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr">
+      <c r="M435" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
+    <row r="436">
+      <c r="A436" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B436" t="inlineStr">
         <is>
           <t>game92scorer</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr">
+      <c r="C436" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr">
+      <c r="D436" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame92} players.</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr">
+      <c r="G436" t="inlineStr">
         <is>
           <t>selected(${game92}, squad)</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
+      <c r="H436" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I404" t="inlineStr">
+      <c r="I436" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame92}</t>
         </is>
       </c>
-      <c r="J404" t="inlineStr">
+      <c r="J436" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame92} players!</t>
         </is>
       </c>
-      <c r="L404" t="inlineStr">
+      <c r="L436" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M404" t="inlineStr">
+      <c r="M436" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame92} != 0</t>
         </is>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
+    <row r="437">
+      <c r="A437" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>scoregame93</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
+      <c r="C437" t="inlineStr">
         <is>
           <t>Round of 16 : Portugal vs Spain</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
+      <c r="D437" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I405" t="inlineStr">
+      <c r="I437" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J405" t="inlineStr">
+      <c r="J437" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L405" t="inlineStr">
+      <c r="L437" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M405" t="inlineStr">
+      <c r="M437" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
+    <row r="438">
+      <c r="A438" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>sumgoalgame93</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
+      <c r="C438" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr">
+      <c r="K438" t="inlineStr">
         <is>
           <t>substr(${scoregame93}, 0, 1) + substr(${scoregame93}, 2, 4)</t>
         </is>
       </c>
-      <c r="M406" t="inlineStr">
+      <c r="M438" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
+    <row r="439">
+      <c r="A439" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
+      <c r="B439" t="inlineStr">
         <is>
           <t>diffgoalgame93</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr">
+      <c r="C439" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr">
+      <c r="K439" t="inlineStr">
         <is>
           <t>substr(${scoregame93}, 0, 1) - substr(${scoregame93}, 2, 4)</t>
         </is>
       </c>
-      <c r="M407" t="inlineStr">
+      <c r="M439" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
+    <row r="440">
+      <c r="A440" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B440" t="inlineStr">
         <is>
           <t>resultgamegame93</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr">
+      <c r="C440" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr">
+      <c r="K440" t="inlineStr">
         <is>
           <t>if(${diffgoalgame93} &gt; 0, 'Portugal  wins!!! ', if(${diffgoalgame93} = 0, 'Portugal and Spain  draw!!! ', if(${diffgoalgame93} &lt; 0, 'Spain  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M408" t="inlineStr">
+      <c r="M440" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
+    <row r="441">
+      <c r="A441" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>notegame93</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C441" t="inlineStr">
         <is>
           <t>${resultgamegame93} ${scoregame93}</t>
         </is>
       </c>
-      <c r="M409" t="inlineStr">
+      <c r="M441" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
+    <row r="442">
+      <c r="A442" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
+      <c r="B442" t="inlineStr">
         <is>
           <t>drawgame93</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
+      <c r="C442" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
+      <c r="D442" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr">
+      <c r="G442" t="inlineStr">
         <is>
           <t>selected(${game93}, squad)</t>
         </is>
       </c>
-      <c r="J410" t="inlineStr">
+      <c r="J442" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L410" t="inlineStr">
+      <c r="L442" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M410" t="inlineStr">
+      <c r="M442" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${diffgoalgame93} = 0</t>
         </is>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
+    <row r="443">
+      <c r="A443" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B443" t="inlineStr">
         <is>
           <t>game93</t>
         </is>
       </c>
-      <c r="F411" t="inlineStr">
+      <c r="F443" t="inlineStr">
         <is>
           <t>PRT ESP</t>
         </is>
       </c>
-      <c r="M411" t="inlineStr">
+      <c r="M443" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
+    <row r="444">
+      <c r="A444" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B444" t="inlineStr">
         <is>
           <t>game93scorer</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr">
+      <c r="C444" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr">
+      <c r="D444" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame93} players.</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr">
+      <c r="G444" t="inlineStr">
         <is>
           <t>selected(${game93}, squad)</t>
         </is>
       </c>
-      <c r="H412" t="inlineStr">
+      <c r="H444" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr">
+      <c r="I444" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame93}</t>
         </is>
       </c>
-      <c r="J412" t="inlineStr">
+      <c r="J444" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame93} players!</t>
         </is>
       </c>
-      <c r="L412" t="inlineStr">
+      <c r="L444" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M412" t="inlineStr">
+      <c r="M444" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame93} != 0</t>
         </is>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
+    <row r="445">
+      <c r="A445" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B445" t="inlineStr">
         <is>
           <t>scoregame94</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr">
+      <c r="C445" t="inlineStr">
         <is>
           <t>Round of 16 : USA vs Belgium</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr">
+      <c r="D445" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I413" t="inlineStr">
+      <c r="I445" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J413" t="inlineStr">
+      <c r="J445" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L413" t="inlineStr">
+      <c r="L445" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M413" t="inlineStr">
+      <c r="M445" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
+    <row r="446">
+      <c r="A446" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B446" t="inlineStr">
         <is>
           <t>sumgoalgame94</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C446" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr">
+      <c r="K446" t="inlineStr">
         <is>
           <t>substr(${scoregame94}, 0, 1) + substr(${scoregame94}, 2, 4)</t>
         </is>
       </c>
-      <c r="M414" t="inlineStr">
+      <c r="M446" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
+    <row r="447">
+      <c r="A447" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B447" t="inlineStr">
         <is>
           <t>diffgoalgame94</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr">
+      <c r="C447" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr">
+      <c r="K447" t="inlineStr">
         <is>
           <t>substr(${scoregame94}, 0, 1) - substr(${scoregame94}, 2, 4)</t>
         </is>
       </c>
-      <c r="M415" t="inlineStr">
+      <c r="M447" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
+    <row r="448">
+      <c r="A448" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>resultgamegame94</t>
         </is>
       </c>
-      <c r="C416" t="inlineStr">
+      <c r="C448" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr">
+      <c r="K448" t="inlineStr">
         <is>
           <t>if(${diffgoalgame94} &gt; 0, 'USA  wins!!! ', if(${diffgoalgame94} = 0, 'USA and Belgium  draw!!! ', if(${diffgoalgame94} &lt; 0, 'Belgium  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M416" t="inlineStr">
+      <c r="M448" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
+    <row r="449">
+      <c r="A449" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
+      <c r="B449" t="inlineStr">
         <is>
           <t>notegame94</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr">
+      <c r="C449" t="inlineStr">
         <is>
           <t>${resultgamegame94} ${scoregame94}</t>
         </is>
       </c>
-      <c r="M417" t="inlineStr">
+      <c r="M449" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
+    <row r="450">
+      <c r="A450" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>drawgame94</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr">
+      <c r="C450" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
+      <c r="D450" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr">
+      <c r="G450" t="inlineStr">
         <is>
           <t>selected(${game94}, squad)</t>
         </is>
       </c>
-      <c r="J418" t="inlineStr">
+      <c r="J450" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr">
+      <c r="L450" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M418" t="inlineStr">
+      <c r="M450" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${diffgoalgame94} = 0</t>
         </is>
       </c>
     </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
+    <row r="451">
+      <c r="A451" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>game94</t>
         </is>
       </c>
-      <c r="F419" t="inlineStr">
+      <c r="F451" t="inlineStr">
         <is>
           <t>USA BEL</t>
         </is>
       </c>
-      <c r="M419" t="inlineStr">
+      <c r="M451" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
+    <row r="452">
+      <c r="A452" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>game94scorer</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr">
+      <c r="C452" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
+      <c r="D452" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame94} players.</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr">
+      <c r="G452" t="inlineStr">
         <is>
           <t>selected(${game94}, squad)</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
+      <c r="H452" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I420" t="inlineStr">
+      <c r="I452" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame94}</t>
         </is>
       </c>
-      <c r="J420" t="inlineStr">
+      <c r="J452" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame94} players!</t>
         </is>
       </c>
-      <c r="L420" t="inlineStr">
+      <c r="L452" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr">
+      <c r="M452" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame94} != 0</t>
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
+    <row r="453">
+      <c r="A453" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B453" t="inlineStr">
         <is>
           <t>scoregame95</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
+      <c r="C453" t="inlineStr">
         <is>
           <t>Round of 16 : Argentina vs Egypt</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
+      <c r="D453" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I421" t="inlineStr">
+      <c r="I453" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J421" t="inlineStr">
+      <c r="J453" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr">
+      <c r="L453" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M421" t="inlineStr">
+      <c r="M453" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
+    <row r="454">
+      <c r="A454" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B454" t="inlineStr">
         <is>
           <t>sumgoalgame95</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr">
+      <c r="C454" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr">
+      <c r="K454" t="inlineStr">
         <is>
           <t>substr(${scoregame95}, 0, 1) + substr(${scoregame95}, 2, 4)</t>
         </is>
       </c>
-      <c r="M422" t="inlineStr">
+      <c r="M454" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
+    <row r="455">
+      <c r="A455" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
+      <c r="B455" t="inlineStr">
         <is>
           <t>diffgoalgame95</t>
         </is>
       </c>
-      <c r="C423" t="inlineStr">
+      <c r="C455" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr">
+      <c r="K455" t="inlineStr">
         <is>
           <t>substr(${scoregame95}, 0, 1) - substr(${scoregame95}, 2, 4)</t>
         </is>
       </c>
-      <c r="M423" t="inlineStr">
+      <c r="M455" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
+    <row r="456">
+      <c r="A456" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
+      <c r="B456" t="inlineStr">
         <is>
           <t>resultgamegame95</t>
         </is>
       </c>
-      <c r="C424" t="inlineStr">
+      <c r="C456" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr">
+      <c r="K456" t="inlineStr">
         <is>
           <t>if(${diffgoalgame95} &gt; 0, 'Argentina  wins!!! ', if(${diffgoalgame95} = 0, 'Argentina and Egypt  draw!!! ', if(${diffgoalgame95} &lt; 0, 'Egypt  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M424" t="inlineStr">
+      <c r="M456" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
+    <row r="457">
+      <c r="A457" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
+      <c r="B457" t="inlineStr">
         <is>
           <t>notegame95</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr">
+      <c r="C457" t="inlineStr">
         <is>
           <t>${resultgamegame95} ${scoregame95}</t>
         </is>
       </c>
-      <c r="M425" t="inlineStr">
+      <c r="M457" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
+    <row r="458">
+      <c r="A458" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
+      <c r="B458" t="inlineStr">
         <is>
           <t>drawgame95</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
+      <c r="C458" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr">
+      <c r="D458" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
+      <c r="G458" t="inlineStr">
         <is>
           <t>selected(${game95}, squad)</t>
         </is>
       </c>
-      <c r="J426" t="inlineStr">
+      <c r="J458" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr">
+      <c r="L458" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M426" t="inlineStr">
+      <c r="M458" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${diffgoalgame95} = 0</t>
         </is>
       </c>
     </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
+    <row r="459">
+      <c r="A459" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B427" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>game95</t>
         </is>
       </c>
-      <c r="F427" t="inlineStr">
+      <c r="F459" t="inlineStr">
         <is>
           <t>ARG EGY</t>
         </is>
       </c>
-      <c r="M427" t="inlineStr">
+      <c r="M459" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
+    <row r="460">
+      <c r="A460" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
+      <c r="B460" t="inlineStr">
         <is>
           <t>game95scorer</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr">
+      <c r="C460" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr">
+      <c r="D460" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame95} players.</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr">
+      <c r="G460" t="inlineStr">
         <is>
           <t>selected(${game95}, squad)</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
+      <c r="H460" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I428" t="inlineStr">
+      <c r="I460" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame95}</t>
         </is>
       </c>
-      <c r="J428" t="inlineStr">
+      <c r="J460" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame95} players!</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr">
+      <c r="L460" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M428" t="inlineStr">
+      <c r="M460" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame95} != 0</t>
         </is>
       </c>
     </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
+    <row r="461">
+      <c r="A461" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
+      <c r="B461" t="inlineStr">
         <is>
           <t>scoregame96</t>
         </is>
       </c>
-      <c r="C429" t="inlineStr">
+      <c r="C461" t="inlineStr">
         <is>
           <t>Round of 16 : Switzerland vs Colombia</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr">
+      <c r="D461" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I429" t="inlineStr">
+      <c r="I461" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J429" t="inlineStr">
+      <c r="J461" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr">
+      <c r="L461" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M429" t="inlineStr">
+      <c r="M461" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
+    <row r="462">
+      <c r="A462" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
+      <c r="B462" t="inlineStr">
         <is>
           <t>sumgoalgame96</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr">
+      <c r="C462" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr">
+      <c r="K462" t="inlineStr">
         <is>
           <t>substr(${scoregame96}, 0, 1) + substr(${scoregame96}, 2, 4)</t>
         </is>
       </c>
-      <c r="M430" t="inlineStr">
+      <c r="M462" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
+    <row r="463">
+      <c r="A463" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
+      <c r="B463" t="inlineStr">
         <is>
           <t>diffgoalgame96</t>
         </is>
       </c>
-      <c r="C431" t="inlineStr">
+      <c r="C463" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr">
+      <c r="K463" t="inlineStr">
         <is>
           <t>substr(${scoregame96}, 0, 1) - substr(${scoregame96}, 2, 4)</t>
         </is>
       </c>
-      <c r="M431" t="inlineStr">
+      <c r="M463" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
+    <row r="464">
+      <c r="A464" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
+      <c r="B464" t="inlineStr">
         <is>
           <t>resultgamegame96</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr">
+      <c r="C464" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr">
+      <c r="K464" t="inlineStr">
         <is>
           <t>if(${diffgoalgame96} &gt; 0, 'Switzerland  wins!!! ', if(${diffgoalgame96} = 0, 'Switzerland and Colombia  draw!!! ', if(${diffgoalgame96} &lt; 0, 'Colombia  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M432" t="inlineStr">
+      <c r="M464" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
+    <row r="465">
+      <c r="A465" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>notegame96</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
+      <c r="C465" t="inlineStr">
         <is>
           <t>${resultgamegame96} ${scoregame96}</t>
         </is>
       </c>
-      <c r="M433" t="inlineStr">
+      <c r="M465" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
+    <row r="466">
+      <c r="A466" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>drawgame96</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr">
+      <c r="C466" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr">
+      <c r="D466" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr">
+      <c r="G466" t="inlineStr">
         <is>
           <t>selected(${game96}, squad)</t>
         </is>
       </c>
-      <c r="J434" t="inlineStr">
+      <c r="J466" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr">
+      <c r="L466" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M434" t="inlineStr">
+      <c r="M466" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${diffgoalgame96} = 0</t>
         </is>
       </c>
     </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
+    <row r="467">
+      <c r="A467" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>game96</t>
         </is>
       </c>
-      <c r="F435" t="inlineStr">
+      <c r="F467" t="inlineStr">
         <is>
           <t>CHE COL</t>
         </is>
       </c>
-      <c r="M435" t="inlineStr">
+      <c r="M467" t="inlineStr">
         <is>
           <t>${round} = 'r16'</t>
         </is>
       </c>
     </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
+    <row r="468">
+      <c r="A468" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
+      <c r="B468" t="inlineStr">
         <is>
           <t>game96scorer</t>
         </is>
       </c>
-      <c r="C436" t="inlineStr">
+      <c r="C468" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr">
+      <c r="D468" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame96} players.</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr">
+      <c r="G468" t="inlineStr">
         <is>
           <t>selected(${game96}, squad)</t>
         </is>
       </c>
-      <c r="H436" t="inlineStr">
+      <c r="H468" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I436" t="inlineStr">
+      <c r="I468" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame96}</t>
         </is>
       </c>
-      <c r="J436" t="inlineStr">
+      <c r="J468" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame96} players!</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr">
+      <c r="L468" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M436" t="inlineStr">
+      <c r="M468" t="inlineStr">
         <is>
           <t>${round} = 'r16' and ${sumgoalgame96} != 0</t>
         </is>
       </c>
     </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
+    <row r="469">
+      <c r="A469" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B469" t="inlineStr">
         <is>
           <t>scoregame73</t>
         </is>
       </c>
-      <c r="C437" t="inlineStr">
+      <c r="C469" t="inlineStr">
         <is>
           <t>Round of 32 : South Africa vs Canada</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
+      <c r="D469" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I437" t="inlineStr">
+      <c r="I469" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J437" t="inlineStr">
+      <c r="J469" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr">
+      <c r="L469" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M437" t="inlineStr">
+      <c r="M469" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
+    <row r="470">
+      <c r="A470" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
+      <c r="B470" t="inlineStr">
         <is>
           <t>sumgoalgame73</t>
         </is>
       </c>
-      <c r="C438" t="inlineStr">
+      <c r="C470" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr">
+      <c r="K470" t="inlineStr">
         <is>
           <t>substr(${scoregame73}, 0, 1) + substr(${scoregame73}, 2, 4)</t>
         </is>
       </c>
-      <c r="M438" t="inlineStr">
+      <c r="M470" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
+    <row r="471">
+      <c r="A471" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
+      <c r="B471" t="inlineStr">
         <is>
           <t>diffgoalgame73</t>
         </is>
       </c>
-      <c r="C439" t="inlineStr">
+      <c r="C471" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr">
+      <c r="K471" t="inlineStr">
         <is>
           <t>substr(${scoregame73}, 0, 1) - substr(${scoregame73}, 2, 4)</t>
         </is>
       </c>
-      <c r="M439" t="inlineStr">
+      <c r="M471" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
+    <row r="472">
+      <c r="A472" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B472" t="inlineStr">
         <is>
           <t>resultgamegame73</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
+      <c r="C472" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr">
+      <c r="K472" t="inlineStr">
         <is>
           <t>if(${diffgoalgame73} &gt; 0, 'South Africa  wins!!! ', if(${diffgoalgame73} = 0, 'South Africa and Canada  draw!!! ', if(${diffgoalgame73} &lt; 0, 'Canada  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M440" t="inlineStr">
+      <c r="M472" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
+    <row r="473">
+      <c r="A473" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
+      <c r="B473" t="inlineStr">
         <is>
           <t>notegame73</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
+      <c r="C473" t="inlineStr">
         <is>
           <t>${resultgamegame73} ${scoregame73}</t>
         </is>
       </c>
-      <c r="M441" t="inlineStr">
+      <c r="M473" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
+    <row r="474">
+      <c r="A474" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
+      <c r="B474" t="inlineStr">
         <is>
           <t>drawgame73</t>
         </is>
       </c>
-      <c r="C442" t="inlineStr">
+      <c r="C474" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
+      <c r="D474" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G442" t="inlineStr">
+      <c r="G474" t="inlineStr">
         <is>
           <t>selected(${game73}, squad)</t>
         </is>
       </c>
-      <c r="J442" t="inlineStr">
+      <c r="J474" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr">
+      <c r="L474" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M442" t="inlineStr">
+      <c r="M474" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame73} = 0</t>
         </is>
       </c>
     </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
+    <row r="475">
+      <c r="A475" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
+      <c r="B475" t="inlineStr">
         <is>
           <t>game73</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr">
+      <c r="F475" t="inlineStr">
         <is>
           <t>ZAF CAN</t>
         </is>
       </c>
-      <c r="M443" t="inlineStr">
+      <c r="M475" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
+    <row r="476">
+      <c r="A476" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
+      <c r="B476" t="inlineStr">
         <is>
           <t>game73scorer</t>
         </is>
       </c>
-      <c r="C444" t="inlineStr">
+      <c r="C476" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr">
+      <c r="D476" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame73} players.</t>
         </is>
       </c>
-      <c r="G444" t="inlineStr">
+      <c r="G476" t="inlineStr">
         <is>
           <t>selected(${game73}, squad)</t>
         </is>
       </c>
-      <c r="H444" t="inlineStr">
+      <c r="H476" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I444" t="inlineStr">
+      <c r="I476" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame73}</t>
         </is>
       </c>
-      <c r="J444" t="inlineStr">
+      <c r="J476" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame73} players!</t>
         </is>
       </c>
-      <c r="L444" t="inlineStr">
+      <c r="L476" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M444" t="inlineStr">
+      <c r="M476" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame73} != 0</t>
         </is>
       </c>
     </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
+    <row r="477">
+      <c r="A477" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
+      <c r="B477" t="inlineStr">
         <is>
           <t>scoregame74</t>
         </is>
       </c>
-      <c r="C445" t="inlineStr">
+      <c r="C477" t="inlineStr">
         <is>
           <t>Round of 32 : Germany vs Paraguay</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
+      <c r="D477" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I445" t="inlineStr">
+      <c r="I477" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J445" t="inlineStr">
+      <c r="J477" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L445" t="inlineStr">
+      <c r="L477" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M445" t="inlineStr">
+      <c r="M477" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
+    <row r="478">
+      <c r="A478" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
+      <c r="B478" t="inlineStr">
         <is>
           <t>sumgoalgame74</t>
         </is>
       </c>
-      <c r="C446" t="inlineStr">
+      <c r="C478" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr">
+      <c r="K478" t="inlineStr">
         <is>
           <t>substr(${scoregame74}, 0, 1) + substr(${scoregame74}, 2, 4)</t>
         </is>
       </c>
-      <c r="M446" t="inlineStr">
+      <c r="M478" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
+    <row r="479">
+      <c r="A479" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
+      <c r="B479" t="inlineStr">
         <is>
           <t>diffgoalgame74</t>
         </is>
       </c>
-      <c r="C447" t="inlineStr">
+      <c r="C479" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr">
+      <c r="K479" t="inlineStr">
         <is>
           <t>substr(${scoregame74}, 0, 1) - substr(${scoregame74}, 2, 4)</t>
         </is>
       </c>
-      <c r="M447" t="inlineStr">
+      <c r="M479" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>resultgamegame74</t>
         </is>
       </c>
-      <c r="C448" t="inlineStr">
+      <c r="C480" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr">
+      <c r="K480" t="inlineStr">
         <is>
           <t>if(${diffgoalgame74} &gt; 0, 'Germany  wins!!! ', if(${diffgoalgame74} = 0, 'Germany and Paraguay  draw!!! ', if(${diffgoalgame74} &lt; 0, 'Paraguay  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M448" t="inlineStr">
+      <c r="M480" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
+      <c r="B481" t="inlineStr">
         <is>
           <t>notegame74</t>
         </is>
       </c>
-      <c r="C449" t="inlineStr">
+      <c r="C481" t="inlineStr">
         <is>
           <t>${resultgamegame74} ${scoregame74}</t>
         </is>
       </c>
-      <c r="M449" t="inlineStr">
+      <c r="M481" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
+      <c r="B482" t="inlineStr">
         <is>
           <t>drawgame74</t>
         </is>
       </c>
-      <c r="C450" t="inlineStr">
+      <c r="C482" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr">
+      <c r="D482" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G450" t="inlineStr">
+      <c r="G482" t="inlineStr">
         <is>
           <t>selected(${game74}, squad)</t>
         </is>
       </c>
-      <c r="J450" t="inlineStr">
+      <c r="J482" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L450" t="inlineStr">
+      <c r="L482" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M450" t="inlineStr">
+      <c r="M482" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame74} = 0</t>
         </is>
       </c>
     </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
+    <row r="483">
+      <c r="A483" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
+      <c r="B483" t="inlineStr">
         <is>
           <t>game74</t>
         </is>
       </c>
-      <c r="F451" t="inlineStr">
+      <c r="F483" t="inlineStr">
         <is>
           <t>DEU PRY</t>
         </is>
       </c>
-      <c r="M451" t="inlineStr">
+      <c r="M483" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
+    <row r="484">
+      <c r="A484" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
+      <c r="B484" t="inlineStr">
         <is>
           <t>game74scorer</t>
         </is>
       </c>
-      <c r="C452" t="inlineStr">
+      <c r="C484" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr">
+      <c r="D484" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame74} players.</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr">
+      <c r="G484" t="inlineStr">
         <is>
           <t>selected(${game74}, squad)</t>
         </is>
       </c>
-      <c r="H452" t="inlineStr">
+      <c r="H484" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I452" t="inlineStr">
+      <c r="I484" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame74}</t>
         </is>
       </c>
-      <c r="J452" t="inlineStr">
+      <c r="J484" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame74} players!</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr">
+      <c r="L484" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M452" t="inlineStr">
+      <c r="M484" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame74} != 0</t>
         </is>
       </c>
     </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
+    <row r="485">
+      <c r="A485" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>scoregame75</t>
         </is>
       </c>
-      <c r="C453" t="inlineStr">
+      <c r="C485" t="inlineStr">
         <is>
           <t>Round of 32 : Netherlands vs Morocco</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr">
+      <c r="D485" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I453" t="inlineStr">
+      <c r="I485" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J453" t="inlineStr">
+      <c r="J485" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr">
+      <c r="L485" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M453" t="inlineStr">
+      <c r="M485" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t>sumgoalgame75</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
+      <c r="C486" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr">
+      <c r="K486" t="inlineStr">
         <is>
           <t>substr(${scoregame75}, 0, 1) + substr(${scoregame75}, 2, 4)</t>
         </is>
       </c>
-      <c r="M454" t="inlineStr">
+      <c r="M486" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
+    <row r="487">
+      <c r="A487" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
+      <c r="B487" t="inlineStr">
         <is>
           <t>diffgoalgame75</t>
         </is>
       </c>
-      <c r="C455" t="inlineStr">
+      <c r="C487" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr">
+      <c r="K487" t="inlineStr">
         <is>
           <t>substr(${scoregame75}, 0, 1) - substr(${scoregame75}, 2, 4)</t>
         </is>
       </c>
-      <c r="M455" t="inlineStr">
+      <c r="M487" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
+    <row r="488">
+      <c r="A488" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
+      <c r="B488" t="inlineStr">
         <is>
           <t>resultgamegame75</t>
         </is>
       </c>
-      <c r="C456" t="inlineStr">
+      <c r="C488" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr">
+      <c r="K488" t="inlineStr">
         <is>
           <t>if(${diffgoalgame75} &gt; 0, 'Netherlands  wins!!! ', if(${diffgoalgame75} = 0, 'Netherlands and Morocco  draw!!! ', if(${diffgoalgame75} &lt; 0, 'Morocco  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M456" t="inlineStr">
+      <c r="M488" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
+    <row r="489">
+      <c r="A489" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
+      <c r="B489" t="inlineStr">
         <is>
           <t>notegame75</t>
         </is>
       </c>
-      <c r="C457" t="inlineStr">
+      <c r="C489" t="inlineStr">
         <is>
           <t>${resultgamegame75} ${scoregame75}</t>
         </is>
       </c>
-      <c r="M457" t="inlineStr">
+      <c r="M489" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
+    <row r="490">
+      <c r="A490" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
+      <c r="B490" t="inlineStr">
         <is>
           <t>drawgame75</t>
         </is>
       </c>
-      <c r="C458" t="inlineStr">
+      <c r="C490" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr">
+      <c r="D490" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G458" t="inlineStr">
+      <c r="G490" t="inlineStr">
         <is>
           <t>selected(${game75}, squad)</t>
         </is>
       </c>
-      <c r="J458" t="inlineStr">
+      <c r="J490" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr">
+      <c r="L490" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M458" t="inlineStr">
+      <c r="M490" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame75} = 0</t>
         </is>
       </c>
     </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
+    <row r="491">
+      <c r="A491" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
+      <c r="B491" t="inlineStr">
         <is>
           <t>game75</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr">
+      <c r="F491" t="inlineStr">
         <is>
           <t>NLD MAR</t>
         </is>
       </c>
-      <c r="M459" t="inlineStr">
+      <c r="M491" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
+    <row r="492">
+      <c r="A492" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B460" t="inlineStr">
+      <c r="B492" t="inlineStr">
         <is>
           <t>game75scorer</t>
         </is>
       </c>
-      <c r="C460" t="inlineStr">
+      <c r="C492" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr">
+      <c r="D492" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame75} players.</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr">
+      <c r="G492" t="inlineStr">
         <is>
           <t>selected(${game75}, squad)</t>
         </is>
       </c>
-      <c r="H460" t="inlineStr">
+      <c r="H492" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I460" t="inlineStr">
+      <c r="I492" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame75}</t>
         </is>
       </c>
-      <c r="J460" t="inlineStr">
+      <c r="J492" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame75} players!</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr">
+      <c r="L492" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M460" t="inlineStr">
+      <c r="M492" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame75} != 0</t>
         </is>
       </c>
     </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
+    <row r="493">
+      <c r="A493" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
+      <c r="B493" t="inlineStr">
         <is>
           <t>scoregame76</t>
         </is>
       </c>
-      <c r="C461" t="inlineStr">
+      <c r="C493" t="inlineStr">
         <is>
           <t>Round of 32 : Brazil vs Japan</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr">
+      <c r="D493" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I461" t="inlineStr">
+      <c r="I493" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J461" t="inlineStr">
+      <c r="J493" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr">
+      <c r="L493" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M461" t="inlineStr">
+      <c r="M493" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
+    <row r="494">
+      <c r="A494" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr">
+      <c r="B494" t="inlineStr">
         <is>
           <t>sumgoalgame76</t>
         </is>
       </c>
-      <c r="C462" t="inlineStr">
+      <c r="C494" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr">
+      <c r="K494" t="inlineStr">
         <is>
           <t>substr(${scoregame76}, 0, 1) + substr(${scoregame76}, 2, 4)</t>
         </is>
       </c>
-      <c r="M462" t="inlineStr">
+      <c r="M494" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
+    <row r="495">
+      <c r="A495" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
+      <c r="B495" t="inlineStr">
         <is>
           <t>diffgoalgame76</t>
         </is>
       </c>
-      <c r="C463" t="inlineStr">
+      <c r="C495" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr">
+      <c r="K495" t="inlineStr">
         <is>
           <t>substr(${scoregame76}, 0, 1) - substr(${scoregame76}, 2, 4)</t>
         </is>
       </c>
-      <c r="M463" t="inlineStr">
+      <c r="M495" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
+    <row r="496">
+      <c r="A496" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
+      <c r="B496" t="inlineStr">
         <is>
           <t>resultgamegame76</t>
         </is>
       </c>
-      <c r="C464" t="inlineStr">
+      <c r="C496" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr">
+      <c r="K496" t="inlineStr">
         <is>
           <t>if(${diffgoalgame76} &gt; 0, 'Brazil  wins!!! ', if(${diffgoalgame76} = 0, 'Brazil and Japan  draw!!! ', if(${diffgoalgame76} &lt; 0, 'Japan  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M464" t="inlineStr">
+      <c r="M496" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
+    <row r="497">
+      <c r="A497" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
+      <c r="B497" t="inlineStr">
         <is>
           <t>notegame76</t>
         </is>
       </c>
-      <c r="C465" t="inlineStr">
+      <c r="C497" t="inlineStr">
         <is>
           <t>${resultgamegame76} ${scoregame76}</t>
         </is>
       </c>
-      <c r="M465" t="inlineStr">
+      <c r="M497" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
+    <row r="498">
+      <c r="A498" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
+      <c r="B498" t="inlineStr">
         <is>
           <t>drawgame76</t>
         </is>
       </c>
-      <c r="C466" t="inlineStr">
+      <c r="C498" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr">
+      <c r="D498" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G466" t="inlineStr">
+      <c r="G498" t="inlineStr">
         <is>
           <t>selected(${game76}, squad)</t>
         </is>
       </c>
-      <c r="J466" t="inlineStr">
+      <c r="J498" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr">
+      <c r="L498" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M466" t="inlineStr">
+      <c r="M498" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame76} = 0</t>
         </is>
       </c>
     </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
+    <row r="499">
+      <c r="A499" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
+      <c r="B499" t="inlineStr">
         <is>
           <t>game76</t>
         </is>
       </c>
-      <c r="F467" t="inlineStr">
+      <c r="F499" t="inlineStr">
         <is>
           <t>BRA JPN</t>
         </is>
       </c>
-      <c r="M467" t="inlineStr">
+      <c r="M499" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
+    <row r="500">
+      <c r="A500" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
+      <c r="B500" t="inlineStr">
         <is>
           <t>game76scorer</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
+      <c r="C500" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr">
+      <c r="D500" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame76} players.</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr">
+      <c r="G500" t="inlineStr">
         <is>
           <t>selected(${game76}, squad)</t>
         </is>
       </c>
-      <c r="H468" t="inlineStr">
+      <c r="H500" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I468" t="inlineStr">
+      <c r="I500" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame76}</t>
         </is>
       </c>
-      <c r="J468" t="inlineStr">
+      <c r="J500" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame76} players!</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
+      <c r="L500" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M468" t="inlineStr">
+      <c r="M500" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame76} != 0</t>
         </is>
       </c>
     </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
+    <row r="501">
+      <c r="A501" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
+      <c r="B501" t="inlineStr">
         <is>
           <t>scoregame77</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr">
+      <c r="C501" t="inlineStr">
         <is>
           <t>Round of 32 : France vs Sweden</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr">
+      <c r="D501" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I469" t="inlineStr">
+      <c r="I501" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J469" t="inlineStr">
+      <c r="J501" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
+      <c r="L501" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M469" t="inlineStr">
+      <c r="M501" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
+    <row r="502">
+      <c r="A502" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
+      <c r="B502" t="inlineStr">
         <is>
           <t>sumgoalgame77</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr">
+      <c r="C502" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr">
+      <c r="K502" t="inlineStr">
         <is>
           <t>substr(${scoregame77}, 0, 1) + substr(${scoregame77}, 2, 4)</t>
         </is>
       </c>
-      <c r="M470" t="inlineStr">
+      <c r="M502" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
+    <row r="503">
+      <c r="A503" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
+      <c r="B503" t="inlineStr">
         <is>
           <t>diffgoalgame77</t>
         </is>
       </c>
-      <c r="C471" t="inlineStr">
+      <c r="C503" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr">
+      <c r="K503" t="inlineStr">
         <is>
           <t>substr(${scoregame77}, 0, 1) - substr(${scoregame77}, 2, 4)</t>
         </is>
       </c>
-      <c r="M471" t="inlineStr">
+      <c r="M503" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
+    <row r="504">
+      <c r="A504" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
+      <c r="B504" t="inlineStr">
         <is>
           <t>resultgamegame77</t>
         </is>
       </c>
-      <c r="C472" t="inlineStr">
+      <c r="C504" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr">
+      <c r="K504" t="inlineStr">
         <is>
           <t>if(${diffgoalgame77} &gt; 0, 'France  wins!!! ', if(${diffgoalgame77} = 0, 'France and Sweden  draw!!! ', if(${diffgoalgame77} &lt; 0, 'Sweden  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M472" t="inlineStr">
+      <c r="M504" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
+    <row r="505">
+      <c r="A505" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
+      <c r="B505" t="inlineStr">
         <is>
           <t>notegame77</t>
         </is>
       </c>
-      <c r="C473" t="inlineStr">
+      <c r="C505" t="inlineStr">
         <is>
           <t>${resultgamegame77} ${scoregame77}</t>
         </is>
       </c>
-      <c r="M473" t="inlineStr">
+      <c r="M505" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
+    <row r="506">
+      <c r="A506" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
+      <c r="B506" t="inlineStr">
         <is>
           <t>drawgame77</t>
         </is>
       </c>
-      <c r="C474" t="inlineStr">
+      <c r="C506" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr">
+      <c r="D506" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G474" t="inlineStr">
+      <c r="G506" t="inlineStr">
         <is>
           <t>selected(${game77}, squad)</t>
         </is>
       </c>
-      <c r="J474" t="inlineStr">
+      <c r="J506" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr">
+      <c r="L506" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M474" t="inlineStr">
+      <c r="M506" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame77} = 0</t>
         </is>
       </c>
     </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
+    <row r="507">
+      <c r="A507" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
+      <c r="B507" t="inlineStr">
         <is>
           <t>game77</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr">
+      <c r="F507" t="inlineStr">
         <is>
           <t>FRA SWE</t>
         </is>
       </c>
-      <c r="M475" t="inlineStr">
+      <c r="M507" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
+    <row r="508">
+      <c r="A508" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
+      <c r="B508" t="inlineStr">
         <is>
           <t>game77scorer</t>
         </is>
       </c>
-      <c r="C476" t="inlineStr">
+      <c r="C508" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr">
+      <c r="D508" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame77} players.</t>
         </is>
       </c>
-      <c r="G476" t="inlineStr">
+      <c r="G508" t="inlineStr">
         <is>
           <t>selected(${game77}, squad)</t>
         </is>
       </c>
-      <c r="H476" t="inlineStr">
+      <c r="H508" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr">
+      <c r="I508" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame77}</t>
         </is>
       </c>
-      <c r="J476" t="inlineStr">
+      <c r="J508" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame77} players!</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
+      <c r="L508" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M476" t="inlineStr">
+      <c r="M508" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame77} != 0</t>
         </is>
       </c>
     </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
+    <row r="509">
+      <c r="A509" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
+      <c r="B509" t="inlineStr">
         <is>
           <t>scoregame78</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr">
+      <c r="C509" t="inlineStr">
         <is>
           <t>Round of 32 : Ivory Coast vs Norway</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr">
+      <c r="D509" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I477" t="inlineStr">
+      <c r="I509" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J477" t="inlineStr">
+      <c r="J509" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
+      <c r="L509" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M477" t="inlineStr">
+      <c r="M509" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+    <row r="510">
+      <c r="A510" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
+      <c r="B510" t="inlineStr">
         <is>
           <t>sumgoalgame78</t>
         </is>
       </c>
-      <c r="C478" t="inlineStr">
+      <c r="C510" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr">
+      <c r="K510" t="inlineStr">
         <is>
           <t>substr(${scoregame78}, 0, 1) + substr(${scoregame78}, 2, 4)</t>
         </is>
       </c>
-      <c r="M478" t="inlineStr">
+      <c r="M510" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+    <row r="511">
+      <c r="A511" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B511" t="inlineStr">
         <is>
           <t>diffgoalgame78</t>
         </is>
       </c>
-      <c r="C479" t="inlineStr">
+      <c r="C511" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr">
+      <c r="K511" t="inlineStr">
         <is>
           <t>substr(${scoregame78}, 0, 1) - substr(${scoregame78}, 2, 4)</t>
         </is>
       </c>
-      <c r="M479" t="inlineStr">
+      <c r="M511" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
+    <row r="512">
+      <c r="A512" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
+      <c r="B512" t="inlineStr">
         <is>
           <t>resultgamegame78</t>
         </is>
       </c>
-      <c r="C480" t="inlineStr">
+      <c r="C512" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr">
+      <c r="K512" t="inlineStr">
         <is>
           <t>if(${diffgoalgame78} &gt; 0, 'Ivory Coast  wins!!! ', if(${diffgoalgame78} = 0, 'Ivory Coast and Norway  draw!!! ', if(${diffgoalgame78} &lt; 0, 'Norway  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M480" t="inlineStr">
+      <c r="M512" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
+    <row r="513">
+      <c r="A513" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B513" t="inlineStr">
         <is>
           <t>notegame78</t>
         </is>
       </c>
-      <c r="C481" t="inlineStr">
+      <c r="C513" t="inlineStr">
         <is>
           <t>${resultgamegame78} ${scoregame78}</t>
         </is>
       </c>
-      <c r="M481" t="inlineStr">
+      <c r="M513" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
+    <row r="514">
+      <c r="A514" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
+      <c r="B514" t="inlineStr">
         <is>
           <t>drawgame78</t>
         </is>
       </c>
-      <c r="C482" t="inlineStr">
+      <c r="C514" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr">
+      <c r="D514" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr">
+      <c r="G514" t="inlineStr">
         <is>
           <t>selected(${game78}, squad)</t>
         </is>
       </c>
-      <c r="J482" t="inlineStr">
+      <c r="J514" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
+      <c r="L514" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M482" t="inlineStr">
+      <c r="M514" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame78} = 0</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
+    <row r="515">
+      <c r="A515" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
+      <c r="B515" t="inlineStr">
         <is>
           <t>game78</t>
         </is>
       </c>
-      <c r="F483" t="inlineStr">
+      <c r="F515" t="inlineStr">
         <is>
           <t>CIV NOR</t>
         </is>
       </c>
-      <c r="M483" t="inlineStr">
+      <c r="M515" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
+    <row r="516">
+      <c r="A516" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>game78scorer</t>
         </is>
       </c>
-      <c r="C484" t="inlineStr">
+      <c r="C516" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr">
+      <c r="D516" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame78} players.</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr">
+      <c r="G516" t="inlineStr">
         <is>
           <t>selected(${game78}, squad)</t>
         </is>
       </c>
-      <c r="H484" t="inlineStr">
+      <c r="H516" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I484" t="inlineStr">
+      <c r="I516" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame78}</t>
         </is>
       </c>
-      <c r="J484" t="inlineStr">
+      <c r="J516" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame78} players!</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr">
+      <c r="L516" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M484" t="inlineStr">
+      <c r="M516" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame78} != 0</t>
         </is>
       </c>
     </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
+    <row r="517">
+      <c r="A517" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B517" t="inlineStr">
         <is>
           <t>scoregame79</t>
         </is>
       </c>
-      <c r="C485" t="inlineStr">
+      <c r="C517" t="inlineStr">
         <is>
           <t>Round of 32 : Mexico vs Ecuador</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr">
+      <c r="D517" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I485" t="inlineStr">
+      <c r="I517" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J485" t="inlineStr">
+      <c r="J517" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr">
+      <c r="L517" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M485" t="inlineStr">
+      <c r="M517" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
+    <row r="518">
+      <c r="A518" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
+      <c r="B518" t="inlineStr">
         <is>
           <t>sumgoalgame79</t>
         </is>
       </c>
-      <c r="C486" t="inlineStr">
+      <c r="C518" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr">
+      <c r="K518" t="inlineStr">
         <is>
           <t>substr(${scoregame79}, 0, 1) + substr(${scoregame79}, 2, 4)</t>
         </is>
       </c>
-      <c r="M486" t="inlineStr">
+      <c r="M518" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
+    <row r="519">
+      <c r="A519" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
+      <c r="B519" t="inlineStr">
         <is>
           <t>diffgoalgame79</t>
         </is>
       </c>
-      <c r="C487" t="inlineStr">
+      <c r="C519" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr">
+      <c r="K519" t="inlineStr">
         <is>
           <t>substr(${scoregame79}, 0, 1) - substr(${scoregame79}, 2, 4)</t>
         </is>
       </c>
-      <c r="M487" t="inlineStr">
+      <c r="M519" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
+    <row r="520">
+      <c r="A520" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
+      <c r="B520" t="inlineStr">
         <is>
           <t>resultgamegame79</t>
         </is>
       </c>
-      <c r="C488" t="inlineStr">
+      <c r="C520" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr">
+      <c r="K520" t="inlineStr">
         <is>
           <t>if(${diffgoalgame79} &gt; 0, 'Mexico  wins!!! ', if(${diffgoalgame79} = 0, 'Mexico and Ecuador  draw!!! ', if(${diffgoalgame79} &lt; 0, 'Ecuador  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M488" t="inlineStr">
+      <c r="M520" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
+    <row r="521">
+      <c r="A521" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
+      <c r="B521" t="inlineStr">
         <is>
           <t>notegame79</t>
         </is>
       </c>
-      <c r="C489" t="inlineStr">
+      <c r="C521" t="inlineStr">
         <is>
           <t>${resultgamegame79} ${scoregame79}</t>
         </is>
       </c>
-      <c r="M489" t="inlineStr">
+      <c r="M521" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
+    <row r="522">
+      <c r="A522" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
+      <c r="B522" t="inlineStr">
         <is>
           <t>drawgame79</t>
         </is>
       </c>
-      <c r="C490" t="inlineStr">
+      <c r="C522" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr">
+      <c r="D522" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr">
+      <c r="G522" t="inlineStr">
         <is>
           <t>selected(${game79}, squad)</t>
         </is>
       </c>
-      <c r="J490" t="inlineStr">
+      <c r="J522" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr">
+      <c r="L522" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M490" t="inlineStr">
+      <c r="M522" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame79} = 0</t>
         </is>
       </c>
     </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
+    <row r="523">
+      <c r="A523" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
+      <c r="B523" t="inlineStr">
         <is>
           <t>game79</t>
         </is>
       </c>
-      <c r="F491" t="inlineStr">
+      <c r="F523" t="inlineStr">
         <is>
           <t>MEX ECU</t>
         </is>
       </c>
-      <c r="M491" t="inlineStr">
+      <c r="M523" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
+    <row r="524">
+      <c r="A524" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B524" t="inlineStr">
         <is>
           <t>game79scorer</t>
         </is>
       </c>
-      <c r="C492" t="inlineStr">
+      <c r="C524" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr">
+      <c r="D524" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame79} players.</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr">
+      <c r="G524" t="inlineStr">
         <is>
           <t>selected(${game79}, squad)</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr">
+      <c r="H524" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I492" t="inlineStr">
+      <c r="I524" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame79}</t>
         </is>
       </c>
-      <c r="J492" t="inlineStr">
+      <c r="J524" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame79} players!</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr">
+      <c r="L524" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M492" t="inlineStr">
+      <c r="M524" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame79} != 0</t>
         </is>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
+    <row r="525">
+      <c r="A525" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B525" t="inlineStr">
         <is>
           <t>scoregame80</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
+      <c r="C525" t="inlineStr">
         <is>
           <t>Round of 32 : England vs DR Congo</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr">
+      <c r="D525" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I493" t="inlineStr">
+      <c r="I525" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J493" t="inlineStr">
+      <c r="J525" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr">
+      <c r="L525" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M493" t="inlineStr">
+      <c r="M525" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
+    <row r="526">
+      <c r="A526" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B526" t="inlineStr">
         <is>
           <t>sumgoalgame80</t>
         </is>
       </c>
-      <c r="C494" t="inlineStr">
+      <c r="C526" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr">
+      <c r="K526" t="inlineStr">
         <is>
           <t>substr(${scoregame80}, 0, 1) + substr(${scoregame80}, 2, 4)</t>
         </is>
       </c>
-      <c r="M494" t="inlineStr">
+      <c r="M526" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
+    <row r="527">
+      <c r="A527" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B495" t="inlineStr">
+      <c r="B527" t="inlineStr">
         <is>
           <t>diffgoalgame80</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
+      <c r="C527" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr">
+      <c r="K527" t="inlineStr">
         <is>
           <t>substr(${scoregame80}, 0, 1) - substr(${scoregame80}, 2, 4)</t>
         </is>
       </c>
-      <c r="M495" t="inlineStr">
+      <c r="M527" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
+    <row r="528">
+      <c r="A528" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
+      <c r="B528" t="inlineStr">
         <is>
           <t>resultgamegame80</t>
         </is>
       </c>
-      <c r="C496" t="inlineStr">
+      <c r="C528" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr">
+      <c r="K528" t="inlineStr">
         <is>
           <t>if(${diffgoalgame80} &gt; 0, 'England  wins!!! ', if(${diffgoalgame80} = 0, 'England and DR Congo  draw!!! ', if(${diffgoalgame80} &lt; 0, 'DR Congo  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M496" t="inlineStr">
+      <c r="M528" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
+    <row r="529">
+      <c r="A529" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B497" t="inlineStr">
+      <c r="B529" t="inlineStr">
         <is>
           <t>notegame80</t>
         </is>
       </c>
-      <c r="C497" t="inlineStr">
+      <c r="C529" t="inlineStr">
         <is>
           <t>${resultgamegame80} ${scoregame80}</t>
         </is>
       </c>
-      <c r="M497" t="inlineStr">
+      <c r="M529" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
+    <row r="530">
+      <c r="A530" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B498" t="inlineStr">
+      <c r="B530" t="inlineStr">
         <is>
           <t>drawgame80</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr">
+      <c r="C530" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr">
+      <c r="D530" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G498" t="inlineStr">
+      <c r="G530" t="inlineStr">
         <is>
           <t>selected(${game80}, squad)</t>
         </is>
       </c>
-      <c r="J498" t="inlineStr">
+      <c r="J530" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr">
+      <c r="L530" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M498" t="inlineStr">
+      <c r="M530" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame80} = 0</t>
         </is>
       </c>
     </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
+    <row r="531">
+      <c r="A531" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B499" t="inlineStr">
+      <c r="B531" t="inlineStr">
         <is>
           <t>game80</t>
         </is>
       </c>
-      <c r="F499" t="inlineStr">
+      <c r="F531" t="inlineStr">
         <is>
           <t>ENG COD</t>
         </is>
       </c>
-      <c r="M499" t="inlineStr">
+      <c r="M531" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
+    <row r="532">
+      <c r="A532" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B500" t="inlineStr">
+      <c r="B532" t="inlineStr">
         <is>
           <t>game80scorer</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
+      <c r="C532" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr">
+      <c r="D532" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame80} players.</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr">
+      <c r="G532" t="inlineStr">
         <is>
           <t>selected(${game80}, squad)</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr">
+      <c r="H532" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I500" t="inlineStr">
+      <c r="I532" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame80}</t>
         </is>
       </c>
-      <c r="J500" t="inlineStr">
+      <c r="J532" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame80} players!</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr">
+      <c r="L532" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M500" t="inlineStr">
+      <c r="M532" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame80} != 0</t>
         </is>
       </c>
     </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
+    <row r="533">
+      <c r="A533" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B501" t="inlineStr">
+      <c r="B533" t="inlineStr">
         <is>
           <t>scoregame81</t>
         </is>
       </c>
-      <c r="C501" t="inlineStr">
+      <c r="C533" t="inlineStr">
         <is>
           <t>Round of 32 : USA vs Bosnia and Herzegovina</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr">
+      <c r="D533" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I501" t="inlineStr">
+      <c r="I533" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J501" t="inlineStr">
+      <c r="J533" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr">
+      <c r="L533" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M501" t="inlineStr">
+      <c r="M533" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
+    <row r="534">
+      <c r="A534" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B502" t="inlineStr">
+      <c r="B534" t="inlineStr">
         <is>
           <t>sumgoalgame81</t>
         </is>
       </c>
-      <c r="C502" t="inlineStr">
+      <c r="C534" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr">
+      <c r="K534" t="inlineStr">
         <is>
           <t>substr(${scoregame81}, 0, 1) + substr(${scoregame81}, 2, 4)</t>
         </is>
       </c>
-      <c r="M502" t="inlineStr">
+      <c r="M534" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
+    <row r="535">
+      <c r="A535" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B503" t="inlineStr">
+      <c r="B535" t="inlineStr">
         <is>
           <t>diffgoalgame81</t>
         </is>
       </c>
-      <c r="C503" t="inlineStr">
+      <c r="C535" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr">
+      <c r="K535" t="inlineStr">
         <is>
           <t>substr(${scoregame81}, 0, 1) - substr(${scoregame81}, 2, 4)</t>
         </is>
       </c>
-      <c r="M503" t="inlineStr">
+      <c r="M535" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
+    <row r="536">
+      <c r="A536" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B504" t="inlineStr">
+      <c r="B536" t="inlineStr">
         <is>
           <t>resultgamegame81</t>
         </is>
       </c>
-      <c r="C504" t="inlineStr">
+      <c r="C536" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr">
+      <c r="K536" t="inlineStr">
         <is>
           <t>if(${diffgoalgame81} &gt; 0, 'USA  wins!!! ', if(${diffgoalgame81} = 0, 'USA and Bosnia and Herzegovina  draw!!! ', if(${diffgoalgame81} &lt; 0, 'Bosnia and Herzegovina  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M504" t="inlineStr">
+      <c r="M536" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
+    <row r="537">
+      <c r="A537" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B505" t="inlineStr">
+      <c r="B537" t="inlineStr">
         <is>
           <t>notegame81</t>
         </is>
       </c>
-      <c r="C505" t="inlineStr">
+      <c r="C537" t="inlineStr">
         <is>
           <t>${resultgamegame81} ${scoregame81}</t>
         </is>
       </c>
-      <c r="M505" t="inlineStr">
+      <c r="M537" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
+    <row r="538">
+      <c r="A538" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B506" t="inlineStr">
+      <c r="B538" t="inlineStr">
         <is>
           <t>drawgame81</t>
         </is>
       </c>
-      <c r="C506" t="inlineStr">
+      <c r="C538" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr">
+      <c r="D538" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr">
+      <c r="G538" t="inlineStr">
         <is>
           <t>selected(${game81}, squad)</t>
         </is>
       </c>
-      <c r="J506" t="inlineStr">
+      <c r="J538" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr">
+      <c r="L538" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M506" t="inlineStr">
+      <c r="M538" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame81} = 0</t>
         </is>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
+    <row r="539">
+      <c r="A539" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B507" t="inlineStr">
+      <c r="B539" t="inlineStr">
         <is>
           <t>game81</t>
         </is>
       </c>
-      <c r="F507" t="inlineStr">
+      <c r="F539" t="inlineStr">
         <is>
           <t>USA BIH</t>
         </is>
       </c>
-      <c r="M507" t="inlineStr">
+      <c r="M539" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
+    <row r="540">
+      <c r="A540" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B508" t="inlineStr">
+      <c r="B540" t="inlineStr">
         <is>
           <t>game81scorer</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
+      <c r="C540" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr">
+      <c r="D540" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame81} players.</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr">
+      <c r="G540" t="inlineStr">
         <is>
           <t>selected(${game81}, squad)</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr">
+      <c r="H540" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr">
+      <c r="I540" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame81}</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr">
+      <c r="J540" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame81} players!</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr">
+      <c r="L540" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M508" t="inlineStr">
+      <c r="M540" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame81} != 0</t>
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
+    <row r="541">
+      <c r="A541" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B509" t="inlineStr">
+      <c r="B541" t="inlineStr">
         <is>
           <t>scoregame82</t>
         </is>
       </c>
-      <c r="C509" t="inlineStr">
+      <c r="C541" t="inlineStr">
         <is>
           <t>Round of 32 : Belgium vs Senegal</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr">
+      <c r="D541" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I509" t="inlineStr">
+      <c r="I541" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J509" t="inlineStr">
+      <c r="J541" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L509" t="inlineStr">
+      <c r="L541" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M509" t="inlineStr">
+      <c r="M541" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
+    <row r="542">
+      <c r="A542" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B510" t="inlineStr">
+      <c r="B542" t="inlineStr">
         <is>
           <t>sumgoalgame82</t>
         </is>
       </c>
-      <c r="C510" t="inlineStr">
+      <c r="C542" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr">
+      <c r="K542" t="inlineStr">
         <is>
           <t>substr(${scoregame82}, 0, 1) + substr(${scoregame82}, 2, 4)</t>
         </is>
       </c>
-      <c r="M510" t="inlineStr">
+      <c r="M542" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
+    <row r="543">
+      <c r="A543" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B511" t="inlineStr">
+      <c r="B543" t="inlineStr">
         <is>
           <t>diffgoalgame82</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
+      <c r="C543" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr">
+      <c r="K543" t="inlineStr">
         <is>
           <t>substr(${scoregame82}, 0, 1) - substr(${scoregame82}, 2, 4)</t>
         </is>
       </c>
-      <c r="M511" t="inlineStr">
+      <c r="M543" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
+    <row r="544">
+      <c r="A544" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B512" t="inlineStr">
+      <c r="B544" t="inlineStr">
         <is>
           <t>resultgamegame82</t>
         </is>
       </c>
-      <c r="C512" t="inlineStr">
+      <c r="C544" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr">
+      <c r="K544" t="inlineStr">
         <is>
           <t>if(${diffgoalgame82} &gt; 0, 'Belgium  wins!!! ', if(${diffgoalgame82} = 0, 'Belgium and Senegal  draw!!! ', if(${diffgoalgame82} &lt; 0, 'Senegal  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M512" t="inlineStr">
+      <c r="M544" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
+    <row r="545">
+      <c r="A545" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B513" t="inlineStr">
+      <c r="B545" t="inlineStr">
         <is>
           <t>notegame82</t>
         </is>
       </c>
-      <c r="C513" t="inlineStr">
+      <c r="C545" t="inlineStr">
         <is>
           <t>${resultgamegame82} ${scoregame82}</t>
         </is>
       </c>
-      <c r="M513" t="inlineStr">
+      <c r="M545" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
+    <row r="546">
+      <c r="A546" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B514" t="inlineStr">
+      <c r="B546" t="inlineStr">
         <is>
           <t>drawgame82</t>
         </is>
       </c>
-      <c r="C514" t="inlineStr">
+      <c r="C546" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr">
+      <c r="D546" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr">
+      <c r="G546" t="inlineStr">
         <is>
           <t>selected(${game82}, squad)</t>
         </is>
       </c>
-      <c r="J514" t="inlineStr">
+      <c r="J546" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr">
+      <c r="L546" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M514" t="inlineStr">
+      <c r="M546" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame82} = 0</t>
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
+    <row r="547">
+      <c r="A547" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B515" t="inlineStr">
+      <c r="B547" t="inlineStr">
         <is>
           <t>game82</t>
         </is>
       </c>
-      <c r="F515" t="inlineStr">
+      <c r="F547" t="inlineStr">
         <is>
           <t>BEL SEN</t>
         </is>
       </c>
-      <c r="M515" t="inlineStr">
+      <c r="M547" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
+    <row r="548">
+      <c r="A548" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B516" t="inlineStr">
+      <c r="B548" t="inlineStr">
         <is>
           <t>game82scorer</t>
         </is>
       </c>
-      <c r="C516" t="inlineStr">
+      <c r="C548" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr">
+      <c r="D548" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame82} players.</t>
         </is>
       </c>
-      <c r="G516" t="inlineStr">
+      <c r="G548" t="inlineStr">
         <is>
           <t>selected(${game82}, squad)</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr">
+      <c r="H548" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I516" t="inlineStr">
+      <c r="I548" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame82}</t>
         </is>
       </c>
-      <c r="J516" t="inlineStr">
+      <c r="J548" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame82} players!</t>
         </is>
       </c>
-      <c r="L516" t="inlineStr">
+      <c r="L548" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M516" t="inlineStr">
+      <c r="M548" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame82} != 0</t>
         </is>
       </c>
     </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B517" t="inlineStr">
+      <c r="B549" t="inlineStr">
         <is>
           <t>scoregame83</t>
         </is>
       </c>
-      <c r="C517" t="inlineStr">
+      <c r="C549" t="inlineStr">
         <is>
           <t>Round of 32 : Portugal vs Croatia</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr">
+      <c r="D549" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I517" t="inlineStr">
+      <c r="I549" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J517" t="inlineStr">
+      <c r="J549" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L517" t="inlineStr">
+      <c r="L549" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M517" t="inlineStr">
+      <c r="M549" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B518" t="inlineStr">
+      <c r="B550" t="inlineStr">
         <is>
           <t>sumgoalgame83</t>
         </is>
       </c>
-      <c r="C518" t="inlineStr">
+      <c r="C550" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr">
+      <c r="K550" t="inlineStr">
         <is>
           <t>substr(${scoregame83}, 0, 1) + substr(${scoregame83}, 2, 4)</t>
         </is>
       </c>
-      <c r="M518" t="inlineStr">
+      <c r="M550" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B519" t="inlineStr">
+      <c r="B551" t="inlineStr">
         <is>
           <t>diffgoalgame83</t>
         </is>
       </c>
-      <c r="C519" t="inlineStr">
+      <c r="C551" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr">
+      <c r="K551" t="inlineStr">
         <is>
           <t>substr(${scoregame83}, 0, 1) - substr(${scoregame83}, 2, 4)</t>
         </is>
       </c>
-      <c r="M519" t="inlineStr">
+      <c r="M551" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B520" t="inlineStr">
+      <c r="B552" t="inlineStr">
         <is>
           <t>resultgamegame83</t>
         </is>
       </c>
-      <c r="C520" t="inlineStr">
+      <c r="C552" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr">
+      <c r="K552" t="inlineStr">
         <is>
           <t>if(${diffgoalgame83} &gt; 0, 'Portugal  wins!!! ', if(${diffgoalgame83} = 0, 'Portugal and Croatia  draw!!! ', if(${diffgoalgame83} &lt; 0, 'Croatia  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M520" t="inlineStr">
+      <c r="M552" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B521" t="inlineStr">
+      <c r="B553" t="inlineStr">
         <is>
           <t>notegame83</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
+      <c r="C553" t="inlineStr">
         <is>
           <t>${resultgamegame83} ${scoregame83}</t>
         </is>
       </c>
-      <c r="M521" t="inlineStr">
+      <c r="M553" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B522" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>drawgame83</t>
         </is>
       </c>
-      <c r="C522" t="inlineStr">
+      <c r="C554" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr">
+      <c r="D554" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G522" t="inlineStr">
+      <c r="G554" t="inlineStr">
         <is>
           <t>selected(${game83}, squad)</t>
         </is>
       </c>
-      <c r="J522" t="inlineStr">
+      <c r="J554" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr">
+      <c r="L554" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M522" t="inlineStr">
+      <c r="M554" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame83} = 0</t>
         </is>
       </c>
     </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B523" t="inlineStr">
+      <c r="B555" t="inlineStr">
         <is>
           <t>game83</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr">
+      <c r="F555" t="inlineStr">
         <is>
           <t>PRT HRV</t>
         </is>
       </c>
-      <c r="M523" t="inlineStr">
+      <c r="M555" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B524" t="inlineStr">
+      <c r="B556" t="inlineStr">
         <is>
           <t>game83scorer</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C556" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr">
+      <c r="D556" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame83} players.</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr">
+      <c r="G556" t="inlineStr">
         <is>
           <t>selected(${game83}, squad)</t>
         </is>
       </c>
-      <c r="H524" t="inlineStr">
+      <c r="H556" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr">
+      <c r="I556" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame83}</t>
         </is>
       </c>
-      <c r="J524" t="inlineStr">
+      <c r="J556" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame83} players!</t>
         </is>
       </c>
-      <c r="L524" t="inlineStr">
+      <c r="L556" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M524" t="inlineStr">
+      <c r="M556" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame83} != 0</t>
         </is>
       </c>
     </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B525" t="inlineStr">
+      <c r="B557" t="inlineStr">
         <is>
           <t>scoregame84</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C557" t="inlineStr">
         <is>
           <t>Round of 32 : Spain vs Austria</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr">
+      <c r="D557" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I525" t="inlineStr">
+      <c r="I557" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J525" t="inlineStr">
+      <c r="J557" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr">
+      <c r="L557" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M525" t="inlineStr">
+      <c r="M557" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B558" t="inlineStr">
         <is>
           <t>sumgoalgame84</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
+      <c r="C558" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr">
+      <c r="K558" t="inlineStr">
         <is>
           <t>substr(${scoregame84}, 0, 1) + substr(${scoregame84}, 2, 4)</t>
         </is>
       </c>
-      <c r="M526" t="inlineStr">
+      <c r="M558" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
+    <row r="559">
+      <c r="A559" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B527" t="inlineStr">
+      <c r="B559" t="inlineStr">
         <is>
           <t>diffgoalgame84</t>
         </is>
       </c>
-      <c r="C527" t="inlineStr">
+      <c r="C559" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr">
+      <c r="K559" t="inlineStr">
         <is>
           <t>substr(${scoregame84}, 0, 1) - substr(${scoregame84}, 2, 4)</t>
         </is>
       </c>
-      <c r="M527" t="inlineStr">
+      <c r="M559" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
+    <row r="560">
+      <c r="A560" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B528" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>resultgamegame84</t>
         </is>
       </c>
-      <c r="C528" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr">
+      <c r="K560" t="inlineStr">
         <is>
           <t>if(${diffgoalgame84} &gt; 0, 'Spain  wins!!! ', if(${diffgoalgame84} = 0, 'Spain and Austria  draw!!! ', if(${diffgoalgame84} &lt; 0, 'Austria  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M528" t="inlineStr">
+      <c r="M560" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B529" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t>notegame84</t>
         </is>
       </c>
-      <c r="C529" t="inlineStr">
+      <c r="C561" t="inlineStr">
         <is>
           <t>${resultgamegame84} ${scoregame84}</t>
         </is>
       </c>
-      <c r="M529" t="inlineStr">
+      <c r="M561" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B530" t="inlineStr">
+      <c r="B562" t="inlineStr">
         <is>
           <t>drawgame84</t>
         </is>
       </c>
-      <c r="C530" t="inlineStr">
+      <c r="C562" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
+      <c r="D562" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr">
+      <c r="G562" t="inlineStr">
         <is>
           <t>selected(${game84}, squad)</t>
         </is>
       </c>
-      <c r="J530" t="inlineStr">
+      <c r="J562" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr">
+      <c r="L562" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M530" t="inlineStr">
+      <c r="M562" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame84} = 0</t>
         </is>
       </c>
     </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
+    <row r="563">
+      <c r="A563" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B531" t="inlineStr">
+      <c r="B563" t="inlineStr">
         <is>
           <t>game84</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr">
+      <c r="F563" t="inlineStr">
         <is>
           <t>ESP AUT</t>
         </is>
       </c>
-      <c r="M531" t="inlineStr">
+      <c r="M563" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
+    <row r="564">
+      <c r="A564" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B532" t="inlineStr">
+      <c r="B564" t="inlineStr">
         <is>
           <t>game84scorer</t>
         </is>
       </c>
-      <c r="C532" t="inlineStr">
+      <c r="C564" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr">
+      <c r="D564" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame84} players.</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr">
+      <c r="G564" t="inlineStr">
         <is>
           <t>selected(${game84}, squad)</t>
         </is>
       </c>
-      <c r="H532" t="inlineStr">
+      <c r="H564" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I532" t="inlineStr">
+      <c r="I564" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame84}</t>
         </is>
       </c>
-      <c r="J532" t="inlineStr">
+      <c r="J564" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame84} players!</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr">
+      <c r="L564" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M532" t="inlineStr">
+      <c r="M564" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame84} != 0</t>
         </is>
       </c>
     </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
+    <row r="565">
+      <c r="A565" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B533" t="inlineStr">
+      <c r="B565" t="inlineStr">
         <is>
           <t>scoregame85</t>
         </is>
       </c>
-      <c r="C533" t="inlineStr">
+      <c r="C565" t="inlineStr">
         <is>
           <t>Round of 32 : Switzerland vs Algeria</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr">
+      <c r="D565" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I533" t="inlineStr">
+      <c r="I565" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J533" t="inlineStr">
+      <c r="J565" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr">
+      <c r="L565" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M533" t="inlineStr">
+      <c r="M565" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B534" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>sumgoalgame85</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr">
+      <c r="C566" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr">
+      <c r="K566" t="inlineStr">
         <is>
           <t>substr(${scoregame85}, 0, 1) + substr(${scoregame85}, 2, 4)</t>
         </is>
       </c>
-      <c r="M534" t="inlineStr">
+      <c r="M566" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B535" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>diffgoalgame85</t>
         </is>
       </c>
-      <c r="C535" t="inlineStr">
+      <c r="C567" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr">
+      <c r="K567" t="inlineStr">
         <is>
           <t>substr(${scoregame85}, 0, 1) - substr(${scoregame85}, 2, 4)</t>
         </is>
       </c>
-      <c r="M535" t="inlineStr">
+      <c r="M567" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B536" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>resultgamegame85</t>
         </is>
       </c>
-      <c r="C536" t="inlineStr">
+      <c r="C568" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr">
+      <c r="K568" t="inlineStr">
         <is>
           <t>if(${diffgoalgame85} &gt; 0, 'Switzerland  wins!!! ', if(${diffgoalgame85} = 0, 'Switzerland and Algeria  draw!!! ', if(${diffgoalgame85} &lt; 0, 'Algeria  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M536" t="inlineStr">
+      <c r="M568" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B537" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>notegame85</t>
         </is>
       </c>
-      <c r="C537" t="inlineStr">
+      <c r="C569" t="inlineStr">
         <is>
           <t>${resultgamegame85} ${scoregame85}</t>
         </is>
       </c>
-      <c r="M537" t="inlineStr">
+      <c r="M569" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B538" t="inlineStr">
+      <c r="B570" t="inlineStr">
         <is>
           <t>drawgame85</t>
         </is>
       </c>
-      <c r="C538" t="inlineStr">
+      <c r="C570" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr">
+      <c r="D570" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G538" t="inlineStr">
+      <c r="G570" t="inlineStr">
         <is>
           <t>selected(${game85}, squad)</t>
         </is>
       </c>
-      <c r="J538" t="inlineStr">
+      <c r="J570" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L538" t="inlineStr">
+      <c r="L570" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M538" t="inlineStr">
+      <c r="M570" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame85} = 0</t>
         </is>
       </c>
     </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B539" t="inlineStr">
+      <c r="B571" t="inlineStr">
         <is>
           <t>game85</t>
         </is>
       </c>
-      <c r="F539" t="inlineStr">
+      <c r="F571" t="inlineStr">
         <is>
           <t>CHE DZA</t>
         </is>
       </c>
-      <c r="M539" t="inlineStr">
+      <c r="M571" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B540" t="inlineStr">
+      <c r="B572" t="inlineStr">
         <is>
           <t>game85scorer</t>
         </is>
       </c>
-      <c r="C540" t="inlineStr">
+      <c r="C572" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr">
+      <c r="D572" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame85} players.</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr">
+      <c r="G572" t="inlineStr">
         <is>
           <t>selected(${game85}, squad)</t>
         </is>
       </c>
-      <c r="H540" t="inlineStr">
+      <c r="H572" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I540" t="inlineStr">
+      <c r="I572" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame85}</t>
         </is>
       </c>
-      <c r="J540" t="inlineStr">
+      <c r="J572" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame85} players!</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr">
+      <c r="L572" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M540" t="inlineStr">
+      <c r="M572" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame85} != 0</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B573" t="inlineStr">
         <is>
           <t>scoregame86</t>
         </is>
       </c>
-      <c r="C541" t="inlineStr">
+      <c r="C573" t="inlineStr">
         <is>
           <t>Round of 32 : Argentina vs Cabo Verde</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr">
+      <c r="D573" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I541" t="inlineStr">
+      <c r="I573" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J541" t="inlineStr">
+      <c r="J573" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr">
+      <c r="L573" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M541" t="inlineStr">
+      <c r="M573" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B542" t="inlineStr">
+      <c r="B574" t="inlineStr">
         <is>
           <t>sumgoalgame86</t>
         </is>
       </c>
-      <c r="C542" t="inlineStr">
+      <c r="C574" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr">
+      <c r="K574" t="inlineStr">
         <is>
           <t>substr(${scoregame86}, 0, 1) + substr(${scoregame86}, 2, 4)</t>
         </is>
       </c>
-      <c r="M542" t="inlineStr">
+      <c r="M574" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B543" t="inlineStr">
+      <c r="B575" t="inlineStr">
         <is>
           <t>diffgoalgame86</t>
         </is>
       </c>
-      <c r="C543" t="inlineStr">
+      <c r="C575" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr">
+      <c r="K575" t="inlineStr">
         <is>
           <t>substr(${scoregame86}, 0, 1) - substr(${scoregame86}, 2, 4)</t>
         </is>
       </c>
-      <c r="M543" t="inlineStr">
+      <c r="M575" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B544" t="inlineStr">
+      <c r="B576" t="inlineStr">
         <is>
           <t>resultgamegame86</t>
         </is>
       </c>
-      <c r="C544" t="inlineStr">
+      <c r="C576" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr">
+      <c r="K576" t="inlineStr">
         <is>
           <t>if(${diffgoalgame86} &gt; 0, 'Argentina  wins!!! ', if(${diffgoalgame86} = 0, 'Argentina and Cabo Verde  draw!!! ', if(${diffgoalgame86} &lt; 0, 'Cabo Verde  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M544" t="inlineStr">
+      <c r="M576" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B545" t="inlineStr">
+      <c r="B577" t="inlineStr">
         <is>
           <t>notegame86</t>
         </is>
       </c>
-      <c r="C545" t="inlineStr">
+      <c r="C577" t="inlineStr">
         <is>
           <t>${resultgamegame86} ${scoregame86}</t>
         </is>
       </c>
-      <c r="M545" t="inlineStr">
+      <c r="M577" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>drawgame86</t>
         </is>
       </c>
-      <c r="C546" t="inlineStr">
+      <c r="C578" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr">
+      <c r="D578" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G546" t="inlineStr">
+      <c r="G578" t="inlineStr">
         <is>
           <t>selected(${game86}, squad)</t>
         </is>
       </c>
-      <c r="J546" t="inlineStr">
+      <c r="J578" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L546" t="inlineStr">
+      <c r="L578" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M546" t="inlineStr">
+      <c r="M578" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame86} = 0</t>
         </is>
       </c>
     </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B547" t="inlineStr">
+      <c r="B579" t="inlineStr">
         <is>
           <t>game86</t>
         </is>
       </c>
-      <c r="F547" t="inlineStr">
+      <c r="F579" t="inlineStr">
         <is>
           <t>ARG CPV</t>
         </is>
       </c>
-      <c r="M547" t="inlineStr">
+      <c r="M579" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B548" t="inlineStr">
+      <c r="B580" t="inlineStr">
         <is>
           <t>game86scorer</t>
         </is>
       </c>
-      <c r="C548" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr">
+      <c r="D580" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame86} players.</t>
         </is>
       </c>
-      <c r="G548" t="inlineStr">
+      <c r="G580" t="inlineStr">
         <is>
           <t>selected(${game86}, squad)</t>
         </is>
       </c>
-      <c r="H548" t="inlineStr">
+      <c r="H580" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I548" t="inlineStr">
+      <c r="I580" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame86}</t>
         </is>
       </c>
-      <c r="J548" t="inlineStr">
+      <c r="J580" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame86} players!</t>
         </is>
       </c>
-      <c r="L548" t="inlineStr">
+      <c r="L580" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M548" t="inlineStr">
+      <c r="M580" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame86} != 0</t>
         </is>
       </c>
     </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B549" t="inlineStr">
+      <c r="B581" t="inlineStr">
         <is>
           <t>scoregame87</t>
         </is>
       </c>
-      <c r="C549" t="inlineStr">
+      <c r="C581" t="inlineStr">
         <is>
           <t>Round of 32 : Colombia vs Ghana</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr">
+      <c r="D581" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I549" t="inlineStr">
+      <c r="I581" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J549" t="inlineStr">
+      <c r="J581" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L549" t="inlineStr">
+      <c r="L581" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M549" t="inlineStr">
+      <c r="M581" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B550" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>sumgoalgame87</t>
         </is>
       </c>
-      <c r="C550" t="inlineStr">
+      <c r="C582" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr">
+      <c r="K582" t="inlineStr">
         <is>
           <t>substr(${scoregame87}, 0, 1) + substr(${scoregame87}, 2, 4)</t>
         </is>
       </c>
-      <c r="M550" t="inlineStr">
+      <c r="M582" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B551" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>diffgoalgame87</t>
         </is>
       </c>
-      <c r="C551" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr">
+      <c r="K583" t="inlineStr">
         <is>
           <t>substr(${scoregame87}, 0, 1) - substr(${scoregame87}, 2, 4)</t>
         </is>
       </c>
-      <c r="M551" t="inlineStr">
+      <c r="M583" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
+      <c r="B584" t="inlineStr">
         <is>
           <t>resultgamegame87</t>
         </is>
       </c>
-      <c r="C552" t="inlineStr">
+      <c r="C584" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr">
+      <c r="K584" t="inlineStr">
         <is>
           <t>if(${diffgoalgame87} &gt; 0, 'Colombia  wins!!! ', if(${diffgoalgame87} = 0, 'Colombia and Ghana  draw!!! ', if(${diffgoalgame87} &lt; 0, 'Ghana  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M552" t="inlineStr">
+      <c r="M584" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B553" t="inlineStr">
+      <c r="B585" t="inlineStr">
         <is>
           <t>notegame87</t>
         </is>
       </c>
-      <c r="C553" t="inlineStr">
+      <c r="C585" t="inlineStr">
         <is>
           <t>${resultgamegame87} ${scoregame87}</t>
         </is>
       </c>
-      <c r="M553" t="inlineStr">
+      <c r="M585" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B554" t="inlineStr">
+      <c r="B586" t="inlineStr">
         <is>
           <t>drawgame87</t>
         </is>
       </c>
-      <c r="C554" t="inlineStr">
+      <c r="C586" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr">
+      <c r="D586" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G554" t="inlineStr">
+      <c r="G586" t="inlineStr">
         <is>
           <t>selected(${game87}, squad)</t>
         </is>
       </c>
-      <c r="J554" t="inlineStr">
+      <c r="J586" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L554" t="inlineStr">
+      <c r="L586" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M554" t="inlineStr">
+      <c r="M586" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame87} = 0</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B555" t="inlineStr">
+      <c r="B587" t="inlineStr">
         <is>
           <t>game87</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr">
+      <c r="F587" t="inlineStr">
         <is>
           <t>COL GHA</t>
         </is>
       </c>
-      <c r="M555" t="inlineStr">
+      <c r="M587" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B588" t="inlineStr">
         <is>
           <t>game87scorer</t>
         </is>
       </c>
-      <c r="C556" t="inlineStr">
+      <c r="C588" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr">
+      <c r="D588" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame87} players.</t>
         </is>
       </c>
-      <c r="G556" t="inlineStr">
+      <c r="G588" t="inlineStr">
         <is>
           <t>selected(${game87}, squad)</t>
         </is>
       </c>
-      <c r="H556" t="inlineStr">
+      <c r="H588" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I556" t="inlineStr">
+      <c r="I588" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame87}</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr">
+      <c r="J588" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame87} players!</t>
         </is>
       </c>
-      <c r="L556" t="inlineStr">
+      <c r="L588" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M556" t="inlineStr">
+      <c r="M588" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame87} != 0</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B589" t="inlineStr">
         <is>
           <t>scoregame88</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C589" t="inlineStr">
         <is>
           <t>Round of 32 : Australia vs Egypt</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr">
+      <c r="D589" t="inlineStr">
         <is>
           <t xml:space="preserve">Register the score in the order of the teams in the title. 
 Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
         </is>
       </c>
-      <c r="I557" t="inlineStr">
+      <c r="I589" t="inlineStr">
         <is>
           <t>regex(., '^[0-9+]-[0-9+]$')</t>
         </is>
       </c>
-      <c r="J557" t="inlineStr">
+      <c r="J589" t="inlineStr">
         <is>
           <t>Use the format number-number</t>
         </is>
       </c>
-      <c r="L557" t="inlineStr">
+      <c r="L589" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M557" t="inlineStr">
+      <c r="M589" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>sumgoalgame88</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C590" t="inlineStr">
         <is>
           <t>calcsumgoal</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr">
+      <c r="K590" t="inlineStr">
         <is>
           <t>substr(${scoregame88}, 0, 1) + substr(${scoregame88}, 2, 4)</t>
         </is>
       </c>
-      <c r="M558" t="inlineStr">
+      <c r="M590" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B591" t="inlineStr">
         <is>
           <t>diffgoalgame88</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C591" t="inlineStr">
         <is>
           <t>calcdiffgoal</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr">
+      <c r="K591" t="inlineStr">
         <is>
           <t>substr(${scoregame88}, 0, 1) - substr(${scoregame88}, 2, 4)</t>
         </is>
       </c>
-      <c r="M559" t="inlineStr">
+      <c r="M591" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t>calculate</t>
         </is>
       </c>
-      <c r="B560" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>resultgamegame88</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C592" t="inlineStr">
         <is>
           <t>resultgame</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr">
+      <c r="K592" t="inlineStr">
         <is>
           <t>if(${diffgoalgame88} &gt; 0, 'Australia  wins!!! ', if(${diffgoalgame88} = 0, 'Australia and Egypt  draw!!! ', if(${diffgoalgame88} &lt; 0, 'Egypt  wins!!!  by  ', 'Please enter a score')))</t>
         </is>
       </c>
-      <c r="M560" t="inlineStr">
+      <c r="M592" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="B561" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>notegame88</t>
         </is>
       </c>
-      <c r="C561" t="inlineStr">
+      <c r="C593" t="inlineStr">
         <is>
           <t>${resultgamegame88} ${scoregame88}</t>
         </is>
       </c>
-      <c r="M561" t="inlineStr">
+      <c r="M593" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t>select_one country</t>
         </is>
       </c>
-      <c r="B562" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>drawgame88</t>
         </is>
       </c>
-      <c r="C562" t="inlineStr">
+      <c r="C594" t="inlineStr">
         <is>
           <t>As you selected a draw, please enter the winning team at penalty shootout</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr">
+      <c r="D594" t="inlineStr">
         <is>
           <t>Select one</t>
         </is>
       </c>
-      <c r="G562" t="inlineStr">
+      <c r="G594" t="inlineStr">
         <is>
           <t>selected(${game88}, squad)</t>
         </is>
       </c>
-      <c r="J562" t="inlineStr">
+      <c r="J594" t="inlineStr">
         <is>
           <t>Select one team only</t>
         </is>
       </c>
-      <c r="L562" t="inlineStr">
+      <c r="L594" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M562" t="inlineStr">
+      <c r="M594" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${diffgoalgame88} = 0</t>
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="B563" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t>game88</t>
         </is>
       </c>
-      <c r="F563" t="inlineStr">
+      <c r="F595" t="inlineStr">
         <is>
           <t>AUS EGY</t>
         </is>
       </c>
-      <c r="M563" t="inlineStr">
+      <c r="M595" t="inlineStr">
         <is>
           <t>${round} = 'r32'</t>
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t>select_multiple players</t>
         </is>
       </c>
-      <c r="B564" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>game88scorer</t>
         </is>
       </c>
-      <c r="C564" t="inlineStr">
+      <c r="C596" t="inlineStr">
         <is>
           <t>Select scorers</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr">
+      <c r="D596" t="inlineStr">
         <is>
           <t>Select scorers, be careful of the number of goals per team you register.
 For this game you can only select ${sumgoalgame88} players.</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr">
+      <c r="G596" t="inlineStr">
         <is>
           <t>selected(${game88}, squad)</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
+      <c r="H596" t="inlineStr">
         <is>
           <t>minimal</t>
         </is>
       </c>
-      <c r="I564" t="inlineStr">
+      <c r="I596" t="inlineStr">
         <is>
           <t>count-selected(.)=${sumgoalgame88}</t>
         </is>
       </c>
-      <c r="J564" t="inlineStr">
+      <c r="J596" t="inlineStr">
         <is>
           <t>Review, you must select only ${sumgoalgame88} players!</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr">
+      <c r="L596" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="M564" t="inlineStr">
+      <c r="M596" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame88} != 0</t>
         </is>

--- a/surveyWCknock.xlsx
+++ b/surveyWCknock.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M596"/>
+  <dimension ref="A1:M612"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>r4</t>
+          <t>r2</t>
         </is>
       </c>
     </row>
@@ -18537,6 +18537,532 @@
       <c r="M596" t="inlineStr">
         <is>
           <t>${round} = 'r32' and ${sumgoalgame88} != 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>scoregame101</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Semifinal : France vs Spain</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Register the score in the order of the teams in the title. 
+Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9+]-[0-9+]$')</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>Use the format number-number</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>sumgoalgame101</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>calcsumgoal</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>substr(${scoregame101}, 0, 1) + substr(${scoregame101}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>diffgoalgame101</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>calcdiffgoal</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>substr(${scoregame101}, 0, 1) - substr(${scoregame101}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>resultgamegame101</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>resultgame</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>if(${diffgoalgame101} &gt; 0, 'France  wins!!! ', if(${diffgoalgame101} = 0, 'France and Spain  draw!!! ', if(${diffgoalgame101} &lt; 0, 'Spain  wins!!!  by  ', 'Please enter a score')))</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>notegame101</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>${resultgamegame101} ${scoregame101}</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>select_one country</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>drawgame101</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>As you selected a draw, please enter the winning team at penalty shootout</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>selected(${game101}, squad)</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>Select one team only</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>${round} = 'r2' and ${diffgoalgame101} = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>game101</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>FRA ESP</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>select_multiple players</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>game101scorer</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Select scorers</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Select scorers, be careful of the number of goals per team you register.
+For this game you can only select ${sumgoalgame101} players.</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>selected(${game101}, squad)</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>count-selected(.)=${sumgoalgame101}</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>Review, you must select only ${sumgoalgame101} players!</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>${round} = 'r2' and ${sumgoalgame101} != 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>scoregame102</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Semifinal : England vs Argentina</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Register the score in the order of the teams in the title. 
+Only numbers separated by a - i.e.:  0-0  ;  3-1 </t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>regex(., '^[0-9+]-[0-9+]$')</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>Use the format number-number</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>sumgoalgame102</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>calcsumgoal</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>substr(${scoregame102}, 0, 1) + substr(${scoregame102}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>diffgoalgame102</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>calcdiffgoal</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>substr(${scoregame102}, 0, 1) - substr(${scoregame102}, 2, 4)</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>resultgamegame102</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>resultgame</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>if(${diffgoalgame102} &gt; 0, 'England  wins!!! ', if(${diffgoalgame102} = 0, 'England and Argentina  draw!!! ', if(${diffgoalgame102} &lt; 0, 'Argentina  wins!!!  by  ', 'Please enter a score')))</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>notegame102</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>${resultgamegame102} ${scoregame102}</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>select_one country</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>drawgame102</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>As you selected a draw, please enter the winning team at penalty shootout</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Select one</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>selected(${game102}, squad)</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>Select one team only</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>${round} = 'r2' and ${diffgoalgame102} = 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>game102</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>ENG ARG</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>${round} = 'r2'</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>select_multiple players</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>game102scorer</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Select scorers</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Select scorers, be careful of the number of goals per team you register.
+For this game you can only select ${sumgoalgame102} players.</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>selected(${game102}, squad)</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>count-selected(.)=${sumgoalgame102}</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>Review, you must select only ${sumgoalgame102} players!</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>${round} = 'r2' and ${sumgoalgame102} != 0</t>
         </is>
       </c>
     </row>
